--- a/reports/SCRUM-101/generated-testcases.xlsx
+++ b/reports/SCRUM-101/generated-testcases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="292">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -58,826 +58,835 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>TC-SCRUM101-001</t>
-  </si>
-  <si>
-    <t>Complete full checkout with a single item</t>
-  </si>
-  <si>
-    <t>FR-01, FR-02, FR-03, FR-04, FR-05, FR-07, FR-08, FR-09, FR-10, FR-14, AC1, AC2, AC3, AC4, BR4</t>
-  </si>
-  <si>
-    <t>TC-SMOKE-01</t>
+    <t>MTC-001</t>
+  </si>
+  <si>
+    <t>Cart displays a single item with full details</t>
+  </si>
+  <si>
+    <t>FR-01, AC1</t>
+  </si>
+  <si>
+    <t>TC-01</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Major</t>
+  </si>
+  <si>
+    <t>Draft</t>
+  </si>
+  <si>
+    <t>Log in as standard_user/secret_sauce.</t>
+  </si>
+  <si>
+    <t>Redirected to /inventory.html (Products page).</t>
+  </si>
+  <si>
+    <t>Suite1;Positive</t>
+  </si>
+  <si>
+    <t>Click 'Add to cart' for 'Sauce Labs Backpack'.</t>
+  </si>
+  <si>
+    <t>Cart badge shows '1'; button label changes to 'Remove'.</t>
+  </si>
+  <si>
+    <t>Click the cart icon to navigate to the cart page.</t>
+  </si>
+  <si>
+    <t>URL is /cart.html; page heading reads 'Your Cart'.</t>
+  </si>
+  <si>
+    <t>Inspect the cart line item.</t>
+  </si>
+  <si>
+    <t>Item name 'Sauce Labs Backpack', description text, price '$29.99', and quantity '1' are all displayed.</t>
+  </si>
+  <si>
+    <t>MTC-002</t>
+  </si>
+  <si>
+    <t>Cart displays multiple items with correct per-item quantities</t>
+  </si>
+  <si>
+    <t>FR-01, AC1, EDGE-06</t>
+  </si>
+  <si>
+    <t>TC-02</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Moderate</t>
+  </si>
+  <si>
+    <t>Log in as standard_user and add 'Sauce Labs Backpack' and 'Sauce Labs Bike Light' to the cart.</t>
+  </si>
+  <si>
+    <t>Cart badge shows '2'.</t>
+  </si>
+  <si>
+    <t>Navigate to the cart page.</t>
+  </si>
+  <si>
+    <t>Both items are listed, each showing name, description, price ($29.99 and $9.99 respectively), and quantity '1'.</t>
+  </si>
+  <si>
+    <t>MTC-003</t>
+  </si>
+  <si>
+    <t>[Discrepancy] Cart page does not display a total price (FR-02 gap)</t>
+  </si>
+  <si>
+    <t>FR-02, AC1</t>
+  </si>
+  <si>
+    <t>TC-03</t>
+  </si>
+  <si>
+    <t>Log in, add 2 items to the cart, navigate to the cart page.</t>
+  </si>
+  <si>
+    <t>Cart page renders only a QTY/Description/Price table plus 'Continue Shopping' and 'Checkout' buttons.</t>
+  </si>
+  <si>
+    <t>Suite1;Discrepancy</t>
+  </si>
+  <si>
+    <t>Search the cart page for any subtotal/tax/total text or element.</t>
+  </si>
+  <si>
+    <t>Expected (Per FR-02): the cart page must display the total price calculation for cart items. Observed (Live Application): no total-price element is present anywhere on cart.html; totals only appear later on the Overview page. Record as a confirmed FR-02 gap, not a script/tooling defect.</t>
+  </si>
+  <si>
+    <t>MTC-004</t>
+  </si>
+  <si>
+    <t>Continue Shopping returns to Products page and preserves cart contents</t>
+  </si>
+  <si>
+    <t>FR-03, AC1</t>
+  </si>
+  <si>
+    <t>TC-04</t>
+  </si>
+  <si>
+    <t>Minor</t>
+  </si>
+  <si>
+    <t>Log in, add 1 item to cart, navigate to the cart page.</t>
+  </si>
+  <si>
+    <t>Item is listed.</t>
+  </si>
+  <si>
+    <t>Click 'Continue Shopping'.</t>
+  </si>
+  <si>
+    <t>Redirected to /inventory.html.</t>
+  </si>
+  <si>
+    <t>Re-open the cart page.</t>
+  </si>
+  <si>
+    <t>The previously added item is still present; cart badge still shows '1'.</t>
+  </si>
+  <si>
+    <t>MTC-005</t>
+  </si>
+  <si>
+    <t>Checkout button navigates to the checkout information page when the cart has items</t>
+  </si>
+  <si>
+    <t>FR-03, FR-04, AC1, AC2</t>
+  </si>
+  <si>
+    <t>TC-05</t>
+  </si>
+  <si>
+    <t>Log in, add at least 1 item, go to the cart page.</t>
+  </si>
+  <si>
+    <t>Checkout button is visible and enabled.</t>
+  </si>
+  <si>
+    <t>Click 'Checkout'.</t>
+  </si>
+  <si>
+    <t>Redirected to /checkout-step-one.html; page heading reads 'Checkout: Your Information'.</t>
+  </si>
+  <si>
+    <t>MTC-006</t>
+  </si>
+  <si>
+    <t>[Discrepancy] Checkout button is clickable with an empty cart (BR3 not enforced)</t>
+  </si>
+  <si>
+    <t>BR3, AC1</t>
+  </si>
+  <si>
+    <t>TC-06</t>
+  </si>
+  <si>
+    <t>Log in as standard_user without adding any items; navigate directly to the cart page.</t>
+  </si>
+  <si>
+    <t>Cart page shows no line items; cart badge shows empty.</t>
+  </si>
+  <si>
+    <t>Click the 'Checkout' button.</t>
+  </si>
+  <si>
+    <t>Expected (Per BR3): 'Cart cannot be empty when proceeding to checkout' - this action should be blocked. Observed (Live Application): the button is enabled and clicking it successfully navigates to /checkout-step-one.html with a blank form. Record as a confirmed BR3 gap, not a test tooling failure.</t>
+  </si>
+  <si>
+    <t>MTC-007</t>
+  </si>
+  <si>
+    <t>Removing an item from the cart updates the badge and cart contents</t>
+  </si>
+  <si>
+    <t>TC-07</t>
+  </si>
+  <si>
+    <t>Log in, add 2 items to cart, go to the cart page.</t>
+  </si>
+  <si>
+    <t>Cart badge shows '2'; both items listed.</t>
+  </si>
+  <si>
+    <t>Click 'Remove' on one of the two items.</t>
+  </si>
+  <si>
+    <t>That item disappears from the list; cart badge decrements to '1'.</t>
+  </si>
+  <si>
+    <t>MTC-008</t>
+  </si>
+  <si>
+    <t>Happy path - valid checkout information proceeds to Overview</t>
+  </si>
+  <si>
+    <t>FR-04, FR-05, FR-07, AC2, AC3</t>
+  </si>
+  <si>
+    <t>TC-08</t>
   </si>
   <si>
     <t>Critical</t>
   </si>
   <si>
-    <t>Draft</t>
-  </si>
-  <si>
-    <t>Navigate to https://www.saucedemo.com and log in with standard_user / secret_sauce.</t>
-  </si>
-  <si>
-    <t>Redirected to /inventory.html; product grid of 6 items visible.</t>
-  </si>
-  <si>
-    <t>Smoke, Positive, EndToEnd</t>
-  </si>
-  <si>
-    <t>Click 'Add to cart' for 'Sauce Labs Backpack'.</t>
-  </si>
-  <si>
-    <t>Cart badge shows '1'; button changes to 'Remove'.</t>
-  </si>
-  <si>
-    <t>Click the cart icon to open the cart page.</t>
-  </si>
-  <si>
-    <t>/cart.html shows 'Sauce Labs Backpack', its description, price $29.99, quantity 1.</t>
-  </si>
-  <si>
-    <t>Click 'Checkout'.</t>
-  </si>
-  <si>
-    <t>Redirected to /checkout-step-one.html; heading 'Checkout: Your Information'; First Name, Last Name, Zip/Postal Code fields visible.</t>
-  </si>
-  <si>
-    <t>Enter First Name 'John', Last Name 'Doe', Zip '12345', click 'Continue'.</t>
-  </si>
-  <si>
-    <t>Redirected to /checkout-step-two.html; heading 'Checkout: Overview'.</t>
-  </si>
-  <si>
-    <t>Review the overview page contents.</t>
-  </si>
-  <si>
-    <t>'Sauce Labs Backpack' qty 1 price $29.99 listed; 'Payment Information: SauceCard #31337'; 'Shipping Information: Free Pony Express Delivery!'; Item total $29.99, Tax $2.40, Total $32.39.</t>
+    <t>Log in, add 1 item to cart, click 'Checkout' from the cart page.</t>
+  </si>
+  <si>
+    <t>On /checkout-step-one.html with First Name, Last Name, Zip/Postal Code fields and Cancel/Continue buttons visible.</t>
+  </si>
+  <si>
+    <t>Suite2;Positive</t>
+  </si>
+  <si>
+    <t>Fill First Name='Jane', Last Name='Smith', Zip/Postal Code='12345'. Click 'Continue'.</t>
+  </si>
+  <si>
+    <t>Redirected to /checkout-step-two.html; no error message is shown.</t>
+  </si>
+  <si>
+    <t>MTC-009</t>
+  </si>
+  <si>
+    <t>Validation - empty First Name shows field-specific required error</t>
+  </si>
+  <si>
+    <t>FR-06, AC2, BR1</t>
+  </si>
+  <si>
+    <t>TC-09</t>
+  </si>
+  <si>
+    <t>Log in, add an item, reach the checkout information page. Leave all fields empty. Click 'Continue'.</t>
+  </si>
+  <si>
+    <t>An error banner appears with the exact text 'Error: First Name is required'. URL remains /checkout-step-one.html (user is not allowed to proceed).</t>
+  </si>
+  <si>
+    <t>Suite2;Negative</t>
+  </si>
+  <si>
+    <t>MTC-010</t>
+  </si>
+  <si>
+    <t>Validation - empty Last Name (First Name filled) shows field-specific required error</t>
+  </si>
+  <si>
+    <t>TC-10</t>
+  </si>
+  <si>
+    <t>On the checkout information page, fill First Name only ('John'). Leave Last Name and Zip empty. Click 'Continue'.</t>
+  </si>
+  <si>
+    <t>Error banner text is exactly 'Error: Last Name is required'. User remains on /checkout-step-one.html.</t>
+  </si>
+  <si>
+    <t>MTC-011</t>
+  </si>
+  <si>
+    <t>Validation - empty Postal Code (First &amp; Last filled) shows field-specific required error</t>
+  </si>
+  <si>
+    <t>TC-11</t>
+  </si>
+  <si>
+    <t>On the checkout information page, fill First Name ('John') and Last Name ('Doe'). Leave Zip/Postal Code empty. Click 'Continue'.</t>
+  </si>
+  <si>
+    <t>Error banner text is exactly 'Error: Postal Code is required'. Note: the live error message says 'Postal Code', not the field label 'Zip/Postal Code' shown on the form - record this label/message wording mismatch (relevant to OQ-01). User remains on /checkout-step-one.html.</t>
+  </si>
+  <si>
+    <t>MTC-012</t>
+  </si>
+  <si>
+    <t>Edge case (EDGE-01) - submitting with all three fields empty only surfaces the first field's error</t>
+  </si>
+  <si>
+    <t>FR-06, AC2, EDGE-01</t>
+  </si>
+  <si>
+    <t>TC-12</t>
+  </si>
+  <si>
+    <t>On a fresh checkout information page, leave First Name, Last Name, and Zip/Postal Code all empty. Click 'Continue' once.</t>
+  </si>
+  <si>
+    <t>Only a single error is shown: 'Error: First Name is required' (validation is sequential/first-invalid-field-wins, not an aggregate list of all missing fields).</t>
+  </si>
+  <si>
+    <t>MTC-013</t>
+  </si>
+  <si>
+    <t>[Discrepancy] Whitespace-only values bypass required-field validation (EDGE-02)</t>
+  </si>
+  <si>
+    <t>AC5, FR-11, EDGE-02</t>
+  </si>
+  <si>
+    <t>TC-13</t>
+  </si>
+  <si>
+    <t>On the checkout information page, enter three spaces ('   ') into First Name, Last Name, and Zip/Postal Code. Click 'Continue'.</t>
+  </si>
+  <si>
+    <t>Expected (Per AC5/FR-11): whitespace-only values should arguably be treated as incomplete/invalid and blocked. Observed (Live Application): no error is shown and the user is redirected to /checkout-step-two.html. Record as a confirmed validation gap.</t>
+  </si>
+  <si>
+    <t>Suite2;Discrepancy</t>
+  </si>
+  <si>
+    <t>MTC-014</t>
+  </si>
+  <si>
+    <t>[Discrepancy] Special characters are accepted without validation error (AC5/FR-11)</t>
+  </si>
+  <si>
+    <t>AC5, FR-11</t>
+  </si>
+  <si>
+    <t>TC-14</t>
+  </si>
+  <si>
+    <t>On the checkout information page, enter First Name='John', Last Name='Doe', Zip/Postal Code='!@#$%^&amp;*()'. Click 'Continue'.</t>
+  </si>
+  <si>
+    <t>Expected (Per AC5/FR-11): special characters should produce a validation error and block progress. Observed (Live Application): no error is shown and the user proceeds to /checkout-step-two.html. Record as a confirmed AC5/FR-11 gap.</t>
+  </si>
+  <si>
+    <t>MTC-015</t>
+  </si>
+  <si>
+    <t>Boundary - very long input in First Name field is accepted without truncation error</t>
+  </si>
+  <si>
+    <t>TC-15</t>
+  </si>
+  <si>
+    <t>On the checkout information page, enter a 300-character string into First Name, valid values in Last Name ('Doe') and Zip ('12345'). Click 'Continue'.</t>
+  </si>
+  <si>
+    <t>Document actual behavior: whether the app accepts the long value and proceeds to Overview, truncates it silently, or shows a length-related error. Flag any silent truncation or overflow/layout break as a defect.</t>
+  </si>
+  <si>
+    <t>Suite2;Edge</t>
+  </si>
+  <si>
+    <t>MTC-016</t>
+  </si>
+  <si>
+    <t>Edge case (EDGE-03) - non-numeric/alphanumeric Zip/Postal Code is accepted</t>
+  </si>
+  <si>
+    <t>AC2, AC5, EDGE-03</t>
+  </si>
+  <si>
+    <t>TC-16</t>
+  </si>
+  <si>
+    <t>On the checkout information page, enter First Name='John', Last Name='Doe', Zip/Postal Code='SW1A 1AA' (UK-style alphanumeric postal code). Click 'Continue'.</t>
+  </si>
+  <si>
+    <t>No format-specific error is shown; the user proceeds to /checkout-step-two.html - confirms the app performs no format/pattern validation on postal code, only a presence check.</t>
+  </si>
+  <si>
+    <t>MTC-017</t>
+  </si>
+  <si>
+    <t>BR5 on checkout information page - Cancel returns user to the Cart page</t>
+  </si>
+  <si>
+    <t>BR5, AC2</t>
+  </si>
+  <si>
+    <t>TC-17</t>
+  </si>
+  <si>
+    <t>Log in, add an item, reach the checkout information page (do not fill any fields).</t>
+  </si>
+  <si>
+    <t>Cancel and Continue buttons are visible.</t>
+  </si>
+  <si>
+    <t>Click 'Cancel'.</t>
+  </si>
+  <si>
+    <t>Redirected to /cart.html. The previously added item is still present in the cart (not cleared). This matches BR5 for this specific page.</t>
+  </si>
+  <si>
+    <t>MTC-018</t>
+  </si>
+  <si>
+    <t>Error banner can be dismissed via its close (X) control</t>
+  </si>
+  <si>
+    <t>FR-06, AC2</t>
+  </si>
+  <si>
+    <t>TC-18</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Trigger the 'Error: First Name is required' message by clicking 'Continue' with all fields empty.</t>
+  </si>
+  <si>
+    <t>Error banner is visible.</t>
+  </si>
+  <si>
+    <t>Click the dismiss/close (X) icon on the error banner.</t>
+  </si>
+  <si>
+    <t>The error banner disappears from the page.</t>
+  </si>
+  <si>
+    <t>MTC-019</t>
+  </si>
+  <si>
+    <t>BR2 - direct URL navigation to checkout information page while logged out redirects to Login</t>
+  </si>
+  <si>
+    <t>BR2, AC2</t>
+  </si>
+  <si>
+    <t>TC-19</t>
+  </si>
+  <si>
+    <t>Ensure no active session (log out if needed, or use a fresh unauthenticated context). Navigate directly to https://www.saucedemo.com/checkout-step-one.html.</t>
+  </si>
+  <si>
+    <t>Redirected to the login page (/). An error banner reads exactly: "Epic sadface: You can only access '/checkout-step-one.html' when you are logged in."</t>
+  </si>
+  <si>
+    <t>MTC-020</t>
+  </si>
+  <si>
+    <t>Happy path - Overview page shows item summary, payment info, and shipping info</t>
+  </si>
+  <si>
+    <t>FR-08, AC3</t>
+  </si>
+  <si>
+    <t>TC-20</t>
+  </si>
+  <si>
+    <t>Log in as standard_user, add 'Sauce Labs Backpack' and 'Sauce Labs Bike Light' to the cart, proceed through Checkout with valid info (First Name/Last Name/Zip all filled).</t>
+  </si>
+  <si>
+    <t>Redirected to /checkout-step-two.html with heading 'Checkout: Overview'.</t>
+  </si>
+  <si>
+    <t>Suite3;Positive</t>
+  </si>
+  <si>
+    <t>Inspect the page content.</t>
+  </si>
+  <si>
+    <t>Both items are listed with name, description, and price. 'Payment Information:' section shows 'SauceCard #31337'. 'Shipping Information:' section shows 'Free Pony Express Delivery!'. Note: do not assert on a payment-method picker (per RISK-04, SauceDemo has no such UI) - only assert on the static payment info text.</t>
+  </si>
+  <si>
+    <t>MTC-021</t>
+  </si>
+  <si>
+    <t>Happy path - Overview page calculates item total, tax, and grand total correctly for a multi-item cart</t>
+  </si>
+  <si>
+    <t>TC-21</t>
+  </si>
+  <si>
+    <t>Add Sauce Labs Backpack ($29.99) and Sauce Labs Bike Light ($9.99) to the cart and proceed to the Overview page with valid checkout info.</t>
+  </si>
+  <si>
+    <t>'Item total:' reads '$39.98' (sum of item prices).</t>
+  </si>
+  <si>
+    <t>Inspect the Tax line.</t>
+  </si>
+  <si>
+    <t>'Tax:' reads a value consistent with the site's tax rate (observed $3.20, i.e. 8% of item total).</t>
+  </si>
+  <si>
+    <t>Inspect the Total line.</t>
+  </si>
+  <si>
+    <t>'Total:' reads the sum of item total + tax (observed '$43.18').</t>
+  </si>
+  <si>
+    <t>MTC-022</t>
+  </si>
+  <si>
+    <t>[Discrepancy] Cancel on the Overview page redirects to Products, not Cart (BR5)</t>
+  </si>
+  <si>
+    <t>BR5, FR-09, AC3</t>
+  </si>
+  <si>
+    <t>TC-22</t>
+  </si>
+  <si>
+    <t>Reach the Overview page (/checkout-step-two.html) via a valid checkout flow with at least 1 item in the cart.</t>
+  </si>
+  <si>
+    <t>Cancel and Finish buttons are visible.</t>
+  </si>
+  <si>
+    <t>Suite3;Discrepancy</t>
+  </si>
+  <si>
+    <t>Expected (Per BR5): '...return to cart' - should redirect to /cart.html. Observed (Live Application): redirects to /inventory.html (Products page) instead. Record as a confirmed BR5 wording/implementation mismatch.</t>
+  </si>
+  <si>
+    <t>Verify cart contents after the redirect.</t>
+  </si>
+  <si>
+    <t>The cart item count is preserved (not cleared) despite the redirect target difference.</t>
+  </si>
+  <si>
+    <t>MTC-023</t>
+  </si>
+  <si>
+    <t>Happy path - Finish button on the Overview page completes the order</t>
+  </si>
+  <si>
+    <t>FR-09, AC3</t>
+  </si>
+  <si>
+    <t>TC-23</t>
+  </si>
+  <si>
+    <t>Reach the Overview page via a valid checkout flow.</t>
+  </si>
+  <si>
+    <t>Finish button is visible and enabled.</t>
   </si>
   <si>
     <t>Click 'Finish'.</t>
   </si>
   <si>
-    <t>Redirected to /checkout-complete.html; heading 'Thank you for your order!' visible; dispatch confirmation text and 'Back Home' button visible; cart badge empty.</t>
-  </si>
-  <si>
-    <t>Click 'Back Home'.</t>
-  </si>
-  <si>
-    <t>Redirected to /inventory.html; cart remains empty.</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-002</t>
-  </si>
-  <si>
-    <t>Complete checkout with multiple items</t>
-  </si>
-  <si>
-    <t>FR-01, FR-02, FR-04, FR-07, FR-08, AC1, AC3, AC4, BR4</t>
-  </si>
-  <si>
-    <t>TC-SMOKE-02</t>
-  </si>
-  <si>
-    <t>Log in as standard_user; add 'Sauce Labs Backpack' and 'Sauce Labs Bike Light' to cart from the inventory page.</t>
-  </si>
-  <si>
-    <t>Cart badge shows '2'.</t>
-  </si>
-  <si>
-    <t>Smoke, Positive, MultiItem</t>
-  </si>
-  <si>
-    <t>Open the cart page and click 'Checkout'.</t>
-  </si>
-  <si>
-    <t>Both items listed with correct name/description/price/qty=1; user reaches /checkout-step-one.html.</t>
-  </si>
-  <si>
-    <t>Enter valid First Name, Last Name, Zip; click 'Continue'.</t>
-  </si>
-  <si>
-    <t>Redirected to /checkout-step-two.html; both items listed in the order summary.</t>
-  </si>
-  <si>
-    <t>Verify the price breakdown.</t>
-  </si>
-  <si>
-    <t>Item total $39.98, Tax $3.20, Total $43.18.</t>
-  </si>
-  <si>
-    <t>Order confirmation page shown with success message; cart badge empty.</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-003</t>
-  </si>
-  <si>
-    <t>Checkout flow is fully blocked without authentication</t>
-  </si>
-  <si>
-    <t>FR-12, BR2</t>
-  </si>
-  <si>
-    <t>TC-SMOKE-03</t>
-  </si>
-  <si>
-    <t>Without logging in, navigate directly to /checkout-step-one.html.</t>
-  </si>
-  <si>
-    <t>Redirected to the login page (/); error alert reads: "Epic sadface: You can only access '/checkout-step-one.html' when you are logged in."</t>
-  </si>
-  <si>
-    <t>Smoke, Negative, Security</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-004</t>
-  </si>
-  <si>
-    <t>Cart page displays complete details for every item</t>
-  </si>
-  <si>
-    <t>FR-01, AC1</t>
-  </si>
-  <si>
-    <t>TC-CART-01</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Log in, add 'Sauce Labs Backpack', 'Sauce Labs Bolt T-Shirt', 'Sauce Labs Onesie' to the cart, then open the cart page.</t>
-  </si>
-  <si>
-    <t>Each of the 3 items shows its name, full description text, unit price, and quantity (1) in the cart table.</t>
-  </si>
-  <si>
-    <t>CartReview, Positive</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-005</t>
-  </si>
-  <si>
-    <t>[DISCREPANCY] Cart page does not display a total price</t>
-  </si>
-  <si>
-    <t>FR-02, AC1</t>
-  </si>
-  <si>
-    <t>TC-CART-02</t>
-  </si>
-  <si>
-    <t>Log in, add two items to the cart, open the cart page.</t>
-  </si>
-  <si>
-    <t>Expected (per requirement - FR-02/AC1): Cart page displays the total price calculation for items in cart. Observed (live behavior): Only each item's individual unit price is shown; no subtotal/item-total/grand-total element exists anywhere on /cart.html; the total only appears later on the Overview page. Confirmed functional gap against FR-02 - flag for stakeholder decision, not a script defect.</t>
-  </si>
-  <si>
-    <t>CartReview, Discrepancy, FunctionalGap</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-006</t>
-  </si>
-  <si>
-    <t>'Continue Shopping' returns to products page without changing cart</t>
-  </si>
-  <si>
-    <t>FR-03, AC1</t>
-  </si>
-  <si>
-    <t>TC-CART-03</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Log in, add one item to the cart, open the cart page, click 'Continue Shopping'.</t>
-  </si>
-  <si>
-    <t>Redirected to /inventory.html; cart badge still shows '1' (cart contents unchanged).</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-007</t>
-  </si>
-  <si>
-    <t>Removing an item from the cart page updates the list and badge</t>
-  </si>
-  <si>
-    <t>AC1 (derived - cart management)</t>
-  </si>
-  <si>
-    <t>TC-CART-04</t>
-  </si>
-  <si>
-    <t>Log in, add two items to the cart, open the cart page, click 'Remove' next to one item.</t>
-  </si>
-  <si>
-    <t>Removed item disappears from the cart list; cart badge decrements from '2' to '1'.</t>
-  </si>
-  <si>
-    <t>CartReview, Positive, EdgeCase</t>
-  </si>
-  <si>
-    <t>Click 'Remove' on the remaining item.</t>
-  </si>
-  <si>
-    <t>Cart list is empty; cart icon shows 'Cart, empty' with no numeric badge.</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-008</t>
-  </si>
-  <si>
-    <t>'Checkout' button on cart page redirects to Checkout Information page</t>
-  </si>
-  <si>
-    <t>FR-04, AC2</t>
-  </si>
-  <si>
-    <t>TC-CHK-01</t>
-  </si>
-  <si>
-    <t>Log in, add an item to the cart, open the cart page, click 'Checkout'.</t>
-  </si>
-  <si>
-    <t>Redirected to /checkout-step-one.html with heading 'Checkout: Your Information' and an empty First Name, Last Name, and Zip/Postal Code form.</t>
-  </si>
-  <si>
-    <t>CheckoutInfo, Positive</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-009</t>
-  </si>
-  <si>
-    <t>Submitting with all fields empty shows First Name required error</t>
-  </si>
-  <si>
-    <t>FR-06, AC2, BR1</t>
-  </si>
-  <si>
-    <t>TC-CHK-02</t>
-  </si>
-  <si>
-    <t>Leave all fields empty and click 'Continue'.</t>
-  </si>
-  <si>
-    <t>User remains on /checkout-step-one.html; error alert reads 'Error: First Name is required'; no other field error is shown simultaneously.</t>
-  </si>
-  <si>
-    <t>CheckoutInfo, Negative, Validation</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-010</t>
-  </si>
-  <si>
-    <t>Submitting with only First Name filled shows Last Name required error</t>
-  </si>
-  <si>
-    <t>TC-CHK-03</t>
-  </si>
-  <si>
-    <t>Enter First Name 'John' only, leave Last Name and Zip empty, click 'Continue'.</t>
-  </si>
-  <si>
-    <t>User remains on /checkout-step-one.html; error alert reads 'Error: Last Name is required'.</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-011</t>
-  </si>
-  <si>
-    <t>Submitting with First and Last Name filled shows Postal Code required error</t>
-  </si>
-  <si>
-    <t>TC-CHK-04</t>
-  </si>
-  <si>
-    <t>Enter First Name 'John' and Last Name 'Doe', leave Zip empty, click 'Continue'.</t>
-  </si>
-  <si>
-    <t>User remains on /checkout-step-one.html; error alert reads 'Error: Postal Code is required'.</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-012</t>
-  </si>
-  <si>
-    <t>Error alert can be dismissed</t>
-  </si>
-  <si>
-    <t>FR-06 (derived UX), AC2</t>
-  </si>
-  <si>
-    <t>TC-CHK-05</t>
-  </si>
-  <si>
-    <t>Trigger a required-field error (submit with all fields empty), then click the 'Dismiss error' (X) icon on the alert.</t>
-  </si>
-  <si>
-    <t>The error alert is removed from the page; form fields remain as previously entered.</t>
-  </si>
-  <si>
-    <t>CheckoutInfo, Positive, UX</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-013</t>
-  </si>
-  <si>
-    <t>[DISCREPANCY] Special characters in Zip/Postal Code are accepted without validation error</t>
-  </si>
-  <si>
-    <t>FR-11, AC5</t>
-  </si>
-  <si>
-    <t>TC-CHK-06</t>
-  </si>
-  <si>
-    <t>Enter First Name 'John', Last Name 'Doe', Zip '!@#$%^&amp;*()', click 'Continue'.</t>
-  </si>
-  <si>
-    <t>Expected (per requirement - AC5/FR-11): An appropriate validation error should be shown and the user should not be able to proceed. Observed (live behavior): No validation error is shown; user is redirected to /checkout-step-two.html as if the input were valid. Confirmed functional gap against AC5 - treat as expected-fail for automation/healing, not a script bug.</t>
-  </si>
-  <si>
-    <t>CheckoutInfo, Discrepancy, Negative, Validation</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-014</t>
-  </si>
-  <si>
-    <t>[DISCREPANCY] Special characters and emoji in First/Last Name are accepted without validation error</t>
-  </si>
-  <si>
-    <t>TC-CHK-07</t>
-  </si>
-  <si>
-    <t>Enter First Name '@@@###', Last Name (emoji string), and a valid Zip, click 'Continue'.</t>
-  </si>
-  <si>
-    <t>Expected (per requirement - AC5/FR-11): A validation error should be shown for invalid/special-character name input. Observed (live behavior): No validation error is shown; user is redirected to /checkout-step-two.html, and the Overview page does not redisplay the name fields for further verification. Confirmed functional gap against AC5.</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-015</t>
-  </si>
-  <si>
-    <t>[BOUNDARY] Excessively long field values are accepted with no visible length limit</t>
-  </si>
-  <si>
-    <t>FR-11 (boundary), AC5</t>
-  </si>
-  <si>
-    <t>TC-CHK-08</t>
-  </si>
-  <si>
-    <t>Enter a 300-character string into First Name, Last Name, and Zip/Postal Code, click 'Continue'.</t>
-  </si>
-  <si>
-    <t>No client-side length-limit error is shown; user is redirected to /checkout-step-two.html. Document actual behavior for stakeholder awareness - no length limit is documented, so this is informational, not a strict pass/fail.</t>
-  </si>
-  <si>
-    <t>CheckoutInfo, Boundary, Informational</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-016</t>
-  </si>
-  <si>
-    <t>Valid data in all fields proceeds to the Overview page</t>
-  </si>
-  <si>
-    <t>FR-05, FR-07, AC2, AC3, BR1</t>
-  </si>
-  <si>
-    <t>TC-CHK-09</t>
-  </si>
-  <si>
-    <t>Enter First Name 'Jane', Last Name 'Smith', Zip '90210', click 'Continue'.</t>
-  </si>
-  <si>
-    <t>Redirected to /checkout-step-two.html with heading 'Checkout: Overview'.</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-017</t>
-  </si>
-  <si>
-    <t>Overview page item summary matches cart contents</t>
-  </si>
-  <si>
-    <t>FR-08, AC3</t>
-  </si>
-  <si>
-    <t>TC-OVW-01</t>
-  </si>
-  <si>
-    <t>Log in, add 'Sauce Labs Fleece Jacket' and 'Sauce Labs Onesie' to the cart, complete valid checkout information, reach the Overview page.</t>
-  </si>
-  <si>
-    <t>Both items listed with correct name, description, price, and quantity, matching what was shown on the cart page.</t>
-  </si>
-  <si>
-    <t>OrderOverview, Positive</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-018</t>
-  </si>
-  <si>
-    <t>Overview page shows static payment and shipping information</t>
-  </si>
-  <si>
-    <t>FR-08, AC3, ASM-04</t>
-  </si>
-  <si>
-    <t>TC-OVW-02</t>
-  </si>
-  <si>
-    <t>Reach the Overview page with any item in the cart.</t>
-  </si>
-  <si>
-    <t>'Payment Information:' section shows 'SauceCard #31337'; 'Shipping Information:' section shows 'Free Pony Express Delivery!'.</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-019</t>
-  </si>
-  <si>
-    <t>[BOUNDARY] Tax and total calculations are correct for 1 item vs. multiple items</t>
-  </si>
-  <si>
-    <t>TC-OVW-03</t>
-  </si>
-  <si>
-    <t>Complete checkout information with only 'Sauce Labs Bike Light' ($9.99) in the cart, reach the Overview page.</t>
-  </si>
-  <si>
-    <t>Item total: $9.99, Tax: $0.80, Total: $10.79 (8% tax rate).</t>
-  </si>
-  <si>
-    <t>OrderOverview, Boundary, Calculation</t>
-  </si>
-  <si>
-    <t>Repeat with 3 items totaling $55.97 (Backpack + Bike Light + Bolt T-Shirt), reach the Overview page.</t>
-  </si>
-  <si>
-    <t>Item total: $55.97, Tax: $4.48, Total: $60.45 - verifying the calculation scales correctly with more items.</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-020</t>
-  </si>
-  <si>
-    <t>Overview page provides Cancel and Finish options</t>
-  </si>
-  <si>
-    <t>FR-09, AC3</t>
-  </si>
-  <si>
-    <t>TC-OVW-04</t>
-  </si>
-  <si>
-    <t>Reach the Overview page with an item in the cart.</t>
-  </si>
-  <si>
-    <t>Both a 'Cancel' button and a 'Finish' button are visible and enabled.</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-021</t>
-  </si>
-  <si>
-    <t>Finish redirects to a confirmation page with a success message</t>
+    <t>Redirected to /checkout-complete.html.</t>
+  </si>
+  <si>
+    <t>MTC-024</t>
+  </si>
+  <si>
+    <t>Happy path - confirmation page shows success message and Back Home button</t>
   </si>
   <si>
     <t>FR-10, AC4</t>
   </si>
   <si>
-    <t>TC-COMP-01</t>
-  </si>
-  <si>
-    <t>Complete the full checkout flow through the Overview page, then click 'Finish'.</t>
-  </si>
-  <si>
-    <t>Redirected to /checkout-complete.html; a 'Pony Express' image, heading 'Thank you for your order!', and dispatch confirmation text are displayed.</t>
-  </si>
-  <si>
-    <t>OrderCompletion, Positive</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-022</t>
-  </si>
-  <si>
-    <t>'Back Home' returns to the Products page</t>
-  </si>
-  <si>
-    <t>TC-COMP-02</t>
+    <t>TC-24</t>
+  </si>
+  <si>
+    <t>Complete a full checkout flow (login -&gt; add item -&gt; cart -&gt; valid checkout info -&gt; Overview -&gt; Finish).</t>
+  </si>
+  <si>
+    <t>On /checkout-complete.html with heading 'Checkout: Complete!'. Text 'Thank you for your order!' is displayed. Supporting text 'Your order has been dispatched, and will arrive just as fast as the pony can get there!' is displayed. A 'Back Home' button is visible.</t>
+  </si>
+  <si>
+    <t>Suite4;Positive</t>
+  </si>
+  <si>
+    <t>MTC-025</t>
+  </si>
+  <si>
+    <t>Back Home button returns the user to the Products page</t>
+  </si>
+  <si>
+    <t>TC-25</t>
   </si>
   <si>
     <t>From the order confirmation page, click 'Back Home'.</t>
   </si>
   <si>
-    <t>Redirected to /inventory.html; the products grid is displayed.</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-023</t>
-  </si>
-  <si>
-    <t>Cart is empty immediately after order completion</t>
-  </si>
-  <si>
-    <t>FR-14, BR4</t>
-  </si>
-  <si>
-    <t>TC-COMP-03</t>
-  </si>
-  <si>
-    <t>Complete a checkout with 2 items in the cart through to the confirmation page.</t>
-  </si>
-  <si>
-    <t>The cart icon shows 'Cart, empty' with no numeric badge on the confirmation page itself, before clicking 'Back Home'.</t>
-  </si>
-  <si>
-    <t>OrderCompletion, BusinessRule, DataIntegrity</t>
-  </si>
-  <si>
-    <t>Navigate to /cart.html directly.</t>
-  </si>
-  <si>
-    <t>Cart page shows no items, confirming BR4/FR-14.</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-024</t>
-  </si>
-  <si>
-    <t>[UNDOCUMENTED FEATURE] 'Generate PDF order' button is present and does not error</t>
-  </si>
-  <si>
-    <t>N/A - undocumented feature (RA report finding #7)</t>
-  </si>
-  <si>
-    <t>TC-COMP-04</t>
-  </si>
-  <si>
-    <t>On the order confirmation page, locate and click 'Generate PDF order'.</t>
-  </si>
-  <si>
-    <t>The action completes without a JavaScript error or broken navigation. Note: this button is not described anywhere in the requirement document; flagged for stakeholder awareness rather than treated as in/out of scope automatically.</t>
-  </si>
-  <si>
-    <t>UndocumentedFeature, Informational</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-025</t>
-  </si>
-  <si>
-    <t>Direct access to Checkout Information page while logged out is blocked</t>
-  </si>
-  <si>
-    <t>TC-BR-01</t>
-  </si>
-  <si>
-    <t>Redirected to the login page; error alert: "Epic sadface: You can only access '/checkout-step-one.html' when you are logged in."</t>
-  </si>
-  <si>
-    <t>BusinessRule, Security, Negative</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-026</t>
-  </si>
-  <si>
-    <t>Direct access to Cart page while logged out is blocked</t>
-  </si>
-  <si>
-    <t>TC-BR-02</t>
-  </si>
-  <si>
-    <t>Without logging in, navigate directly to /cart.html.</t>
-  </si>
-  <si>
-    <t>Redirected to the login page; error alert: "Epic sadface: You can only access '/cart.html' when you are logged in."</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-027</t>
-  </si>
-  <si>
-    <t>[DISCREPANCY] Checkout with an empty cart is not blocked by the application</t>
-  </si>
-  <si>
-    <t>FR-13, BR3</t>
-  </si>
-  <si>
-    <t>TC-BR-03</t>
-  </si>
-  <si>
-    <t>Log in as standard_user with an empty cart, open the cart page.</t>
-  </si>
-  <si>
-    <t>Expected (per requirement - BR3/FR-13): 'Checkout' should be disabled/blocked when the cart is empty. Observed (live behavior): 'Checkout' button is present and enabled despite the cart being empty.</t>
-  </si>
-  <si>
-    <t>BusinessRule, Discrepancy, Negative</t>
-  </si>
-  <si>
-    <t>Click 'Checkout', fill in valid First Name/Last Name/Zip, click 'Continue'.</t>
-  </si>
-  <si>
-    <t>Expected (per requirement): User should not reach the Overview page with an empty cart, or should see a blocking message. Observed (live behavior): User reaches the Overview page showing 'Item total: $0', 'Tax: $0.00', 'Total: $0.00' with no items listed; no blocking message shown.</t>
-  </si>
-  <si>
-    <t>Expected (per requirement): Completing an order with zero items should not be possible. Observed (live behavior): Order confirmation page is shown as if a normal order succeeded. Confirmed functional gap against BR3/FR-13 - classify as an application issue if it fails during healing, not a script bug.</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-028</t>
-  </si>
-  <si>
-    <t>Cancel on Checkout Information page returns to the Cart page</t>
-  </si>
-  <si>
-    <t>FR-15, BR5</t>
-  </si>
-  <si>
-    <t>TC-BR-04</t>
-  </si>
-  <si>
-    <t>Reach the Checkout Information page with an item in the cart, then click 'Cancel'.</t>
-  </si>
-  <si>
-    <t>Redirected to /cart.html; the item added earlier is still present in the cart.</t>
-  </si>
-  <si>
-    <t>BusinessRule, Positive</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-029</t>
-  </si>
-  <si>
-    <t>[DISCREPANCY] Cancel on the Overview page returns to Products, not Cart</t>
-  </si>
-  <si>
-    <t>TC-BR-05</t>
-  </si>
-  <si>
-    <t>Reach the Checkout Overview page (step two) with an item in the cart, then click 'Cancel'.</t>
-  </si>
-  <si>
-    <t>Expected (per requirement - BR5): User should return to the Cart page ('cancel at any step and return to cart'). Observed (live behavior): User is redirected to /inventory.html (Products page), NOT /cart.html - contradicts the literal wording of BR5. Item remains in the cart (verified via /cart.html afterward). Document for stakeholder clarification.</t>
-  </si>
-  <si>
-    <t>BusinessRule, Discrepancy, Navigation</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-030</t>
-  </si>
-  <si>
-    <t>Browser back button from Overview clears entered form data</t>
-  </si>
-  <si>
-    <t>Edge Case (RA report Section 12)</t>
-  </si>
-  <si>
-    <t>TC-NAV-01</t>
-  </si>
-  <si>
-    <t>Reach the Overview page after entering valid checkout information (item in cart).</t>
-  </si>
-  <si>
-    <t>Overview page is displayed correctly.</t>
-  </si>
-  <si>
-    <t>Navigation, EdgeCase</t>
-  </si>
-  <si>
-    <t>Click the browser's Back button.</t>
-  </si>
-  <si>
-    <t>User lands back on /checkout-step-one.html; First Name, Last Name, and Zip fields are all empty (previously entered data is not restored); cart badge still shows the correct item count.</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-031</t>
-  </si>
-  <si>
-    <t>Page refresh mid-checkout clears form data but preserves cart</t>
-  </si>
-  <si>
-    <t>TC-NAV-02</t>
-  </si>
-  <si>
-    <t>On the Checkout Information page, enter First Name and Last Name (leave Zip blank), then refresh the page.</t>
-  </si>
-  <si>
-    <t>Page reloads at /checkout-step-one.html; First Name and Last Name fields are now empty; cart badge count is unchanged from before the refresh.</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-032</t>
-  </si>
-  <si>
-    <t>Direct URL navigation to Checkout Information page works when logged in with items in cart</t>
-  </si>
-  <si>
-    <t>FR-04 (derived/supporting)</t>
-  </si>
-  <si>
-    <t>TC-NAV-03</t>
-  </si>
-  <si>
-    <t>Log in as standard_user, add an item to the cart via the inventory page, then navigate directly to /checkout-step-one.html (bypassing the cart page's Checkout button).</t>
-  </si>
-  <si>
-    <t>The Checkout Information form loads successfully without requiring the user to visit /cart.html first.</t>
-  </si>
-  <si>
-    <t>Navigation, Positive</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-033</t>
-  </si>
-  <si>
-    <t>Logout blocks subsequent access to checkout pages</t>
-  </si>
-  <si>
-    <t>TC-NAV-04</t>
-  </si>
-  <si>
-    <t>Log in as standard_user, open the hamburger menu, and click 'Logout'.</t>
-  </si>
-  <si>
-    <t>User is redirected to the login page (/).</t>
-  </si>
-  <si>
-    <t>Navigation, Security, Negative</t>
-  </si>
-  <si>
-    <t>Attempt to navigate directly to https://www.saucedemo.com/checkout-step-one.html.</t>
-  </si>
-  <si>
-    <t>User is redirected back to the login page with the 'You can only access ... when you are logged in' error, confirming the session was fully terminated.</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-034</t>
-  </si>
-  <si>
-    <t>Cart badge accurately reflects add/remove actions across pages</t>
-  </si>
-  <si>
-    <t>FR-01, FR-02 (derived - UI state consistency)</t>
-  </si>
-  <si>
-    <t>TC-UI-01</t>
-  </si>
-  <si>
-    <t>From the inventory page, add 3 different items one at a time, checking the cart badge after each.</t>
-  </si>
-  <si>
-    <t>Badge increments 1 -&gt; 2 -&gt; 3 correctly after each add.</t>
-  </si>
-  <si>
-    <t>UIValidation, Positive</t>
-  </si>
-  <si>
-    <t>Open the cart page and remove 1 item.</t>
-  </si>
-  <si>
-    <t>Badge updates to '2' immediately, consistent between the header icon and the cart page.</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-035</t>
-  </si>
-  <si>
-    <t>[BOUNDARY] Single item vs. multiple items checkout totals scale correctly</t>
-  </si>
-  <si>
-    <t>FR-08 (boundary)</t>
-  </si>
-  <si>
-    <t>TC-UI-02</t>
-  </si>
-  <si>
-    <t>Complete checkout information with exactly 1 item in the cart and reach the Overview page.</t>
-  </si>
-  <si>
-    <t>Item total equals that single item's price; Tax = 8% of item total (rounded to 2 decimals); Total = item total + tax.</t>
-  </si>
-  <si>
-    <t>UIValidation, Boundary, Calculation</t>
-  </si>
-  <si>
-    <t>Repeat with all 6 available items added to the cart and reach the Overview page.</t>
-  </si>
-  <si>
-    <t>Item total equals the sum of all 6 item prices; Tax and Total are calculated consistently using the same 8% rate.</t>
-  </si>
-  <si>
-    <t>TC-SCRUM101-036</t>
-  </si>
-  <si>
-    <t>[EDGE CASE] Rapid double-click on 'Finish' does not produce a broken or duplicate state</t>
-  </si>
-  <si>
-    <t>Edge Case (RA report Section 12 - idempotency)</t>
-  </si>
-  <si>
-    <t>TC-UI-03</t>
-  </si>
-  <si>
-    <t>Reach the Overview page with a valid cart and checkout information, then double-click the 'Finish' button as fast as possible.</t>
-  </si>
-  <si>
-    <t>User lands on a single, well-formed /checkout-complete.html page with no duplicate confirmation banners, console errors, or broken layout. Record the actual observed behavior - the requirement document defines no explicit idempotency rule for this action, so this documents current behavior for stakeholder awareness rather than asserting a specific pass/fail expectation.</t>
-  </si>
-  <si>
-    <t>UIValidation, EdgeCase, Idempotency</t>
+    <t>Redirected to /inventory.html. Page heading reads 'Products'.</t>
+  </si>
+  <si>
+    <t>MTC-026</t>
+  </si>
+  <si>
+    <t>BR4 - cart is cleared after order confirmation</t>
+  </si>
+  <si>
+    <t>BR4, AC4</t>
+  </si>
+  <si>
+    <t>TC-26</t>
+  </si>
+  <si>
+    <t>Complete a full checkout flow with 2 items in the cart, through to /checkout-complete.html.</t>
+  </si>
+  <si>
+    <t>Cart badge on the confirmation page shows empty (no numeric badge).</t>
+  </si>
+  <si>
+    <t>Click 'Back Home' and open the cart page.</t>
+  </si>
+  <si>
+    <t>Cart page shows zero line items, confirming BR4 is correctly implemented.</t>
+  </si>
+  <si>
+    <t>MTC-027</t>
+  </si>
+  <si>
+    <t>[Discrepancy] Direct URL navigation to checkout information page with an empty cart while logged in (EDGE-04)</t>
+  </si>
+  <si>
+    <t>BR3, EDGE-04</t>
+  </si>
+  <si>
+    <t>TC-27</t>
+  </si>
+  <si>
+    <t>Log in as standard_user. Do not add any items. Navigate directly to https://www.saucedemo.com/checkout-step-one.html.</t>
+  </si>
+  <si>
+    <t>Expected (Per BR3): this should ideally be blocked/redirected given the empty cart. Observed (Live Application): the checkout information form loads normally with an empty cart badge. Record as a confirmed BR3 gap consistent with MTC-006.</t>
+  </si>
+  <si>
+    <t>Suite5;Discrepancy</t>
+  </si>
+  <si>
+    <t>MTC-028</t>
+  </si>
+  <si>
+    <t>Edge case (EDGE-05) - browser Back button from Overview clears entered checkout info but preserves cart</t>
+  </si>
+  <si>
+    <t>EDGE-05</t>
+  </si>
+  <si>
+    <t>TC-28</t>
+  </si>
+  <si>
+    <t>Log in, add 1 item, proceed through checkout info (First Name='Jane', Last Name='Smith', Zip='12345') to the Overview page.</t>
+  </si>
+  <si>
+    <t>On /checkout-step-two.html with the item and totals shown.</t>
+  </si>
+  <si>
+    <t>Suite5;Edge</t>
+  </si>
+  <si>
+    <t>Use the browser's Back navigation (not the in-page Cancel button).</t>
+  </si>
+  <si>
+    <t>Returns to /checkout-step-one.html. First Name, Last Name, and Zip/Postal Code fields are all empty (previously entered values are not restored) - record this as expected/actual behavior for the back-button, since no AC/BR defines it explicitly.</t>
+  </si>
+  <si>
+    <t>Check the cart badge.</t>
+  </si>
+  <si>
+    <t>Cart badge still shows the item added earlier (cart contents are not lost by the back navigation).</t>
+  </si>
+  <si>
+    <t>MTC-029</t>
+  </si>
+  <si>
+    <t>Full end-to-end happy-path regression: Cart -&gt; Checkout Info -&gt; Overview -&gt; Confirmation</t>
+  </si>
+  <si>
+    <t>FR-01, FR-02(gap noted), FR-03, FR-04, FR-05, FR-07, FR-08, FR-09, FR-10, AC1, AC2, AC3, AC4</t>
+  </si>
+  <si>
+    <t>TC-29</t>
+  </si>
+  <si>
+    <t>Suite5;Positive</t>
+  </si>
+  <si>
+    <t>Add 'Sauce Labs Backpack' and 'Sauce Labs Fleece Jacket' to the cart.</t>
+  </si>
+  <si>
+    <t>Open the cart page and verify both items are listed, then click 'Checkout'.</t>
+  </si>
+  <si>
+    <t>Redirected to /checkout-step-one.html.</t>
+  </si>
+  <si>
+    <t>Fill First Name='Alex', Last Name='Rivera', Zip='90210', and click 'Continue'.</t>
+  </si>
+  <si>
+    <t>Redirected to /checkout-step-two.html with no validation errors.</t>
+  </si>
+  <si>
+    <t>Verify the Overview page shows both items, payment/shipping info, and a total of item total ($79.98) plus tax, then click 'Finish'.</t>
+  </si>
+  <si>
+    <t>Verify the success message and click 'Back Home'.</t>
+  </si>
+  <si>
+    <t>'Thank you for your order!' is shown before navigating. After clicking, redirected to /inventory.html and the cart is empty, completing the full regression path.</t>
+  </si>
+  <si>
+    <t>MTC-030</t>
+  </si>
+  <si>
+    <t>BR1 - all three checkout information fields are individually mandatory (combined verification)</t>
+  </si>
+  <si>
+    <t>BR1, FR-05</t>
+  </si>
+  <si>
+    <t>TC-30</t>
+  </si>
+  <si>
+    <t>Reach the checkout information page with an item in the cart. Attempt to submit with only Zip/Postal Code filled (First Name and Last Name empty).</t>
+  </si>
+  <si>
+    <t>Error: 'Error: First Name is required' is shown (first missing mandatory field in DOM order), confirming First Name is enforced as mandatory even when a later field is filled.</t>
+  </si>
+  <si>
+    <t>Suite5;Negative</t>
+  </si>
+  <si>
+    <t>Fill First Name, leave Last Name empty, keep Zip filled. Click 'Continue'.</t>
+  </si>
+  <si>
+    <t>Error: 'Error: Last Name is required' is shown, confirming Last Name is independently mandatory regardless of Zip being filled.</t>
+  </si>
+  <si>
+    <t>Fill First Name and Last Name, clear Zip/Postal Code. Click 'Continue'.</t>
+  </si>
+  <si>
+    <t>Error: 'Error: Postal Code is required' is shown, confirming all three fields are independently mandatory per BR1.</t>
+  </si>
+  <si>
+    <t>MTC-031</t>
+  </si>
+  <si>
+    <t>NFR-01 - Cross-browser regression of the full checkout flow</t>
+  </si>
+  <si>
+    <t>NFR-01</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Repeat the MTC-029 end-to-end regression flow on the latest stable version of Chrome.</t>
+  </si>
+  <si>
+    <t>All steps of MTC-029 pass identically on Chrome.</t>
+  </si>
+  <si>
+    <t>NonFunctional;Blocked-PendingClarification</t>
+  </si>
+  <si>
+    <t>Repeat on the latest stable version of Firefox.</t>
+  </si>
+  <si>
+    <t>All steps of MTC-029 pass identically on Firefox.</t>
+  </si>
+  <si>
+    <t>Repeat on the latest stable version of Safari.</t>
+  </si>
+  <si>
+    <t>All steps of MTC-029 pass identically on Safari.</t>
+  </si>
+  <si>
+    <t>MTC-032</t>
+  </si>
+  <si>
+    <t>NFR-02 - Mobile-responsive checkout regression</t>
+  </si>
+  <si>
+    <t>NFR-02</t>
+  </si>
+  <si>
+    <t>Repeat the MTC-029 end-to-end regression flow at a mobile-portrait viewport.</t>
+  </si>
+  <si>
+    <t>All checkout steps remain usable and visually correct; no layout breakage.</t>
+  </si>
+  <si>
+    <t>Repeat at a mobile-landscape viewport.</t>
+  </si>
+  <si>
+    <t>Same as above.</t>
+  </si>
+  <si>
+    <t>Repeat at a tablet viewport.</t>
+  </si>
+  <si>
+    <t>MTC-033</t>
+  </si>
+  <si>
+    <t>NFR-03 - Usability: clear feedback at each step</t>
+  </si>
+  <si>
+    <t>NFR-03</t>
+  </si>
+  <si>
+    <t>Review the error/feedback messaging already exercised in MTC-009, MTC-010, MTC-011, MTC-012, MTC-018, MTC-020, and MTC-024.</t>
+  </si>
+  <si>
+    <t>Each transition in the checkout flow surfaces a visible confirmation or error message (covered by the referenced test cases). No separate objective usability metric exists to test against.</t>
+  </si>
+  <si>
+    <t>MTC-034</t>
+  </si>
+  <si>
+    <t>NFR-04 - Security of the checkout process</t>
+  </si>
+  <si>
+    <t>NFR-04</t>
+  </si>
+  <si>
+    <t>Attempt to identify any documented security acceptance criterion (e.g., HTTPS enforcement, session handling, input sanitization) in the Requirement Analysis Report.</t>
+  </si>
+  <si>
+    <t>None found - confirms the gap already flagged as RISK-01/OQ-06.</t>
   </si>
 </sst>
 </file>
@@ -1269,10 +1278,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:O68"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="60" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="7" width="12" customWidth="1"/>
@@ -1282,7 +1291,7 @@
     <col min="12" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="49" customWidth="1"/>
+    <col min="15" max="15" width="44" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1349,26 +1358,26 @@
         <v>19</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" s="2">
         <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1388,26 +1397,26 @@
         <v>19</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" s="2">
         <v>2</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1427,26 +1436,26 @@
         <v>19</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H4" s="2">
         <v>3</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1466,2054 +1475,2483 @@
         <v>19</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" s="2">
         <v>4</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H6" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H8" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H9" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" s="2">
         <v>2</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H12" s="2">
         <v>3</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H13" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H14" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H18" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H20" s="2">
         <v>2</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
       <c r="O21" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
       <c r="O23" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H25" s="2">
         <v>1</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
       <c r="O25" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H26" s="2">
         <v>1</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H27" s="2">
         <v>1</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H28" s="2">
         <v>1</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
       <c r="O29" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H30" s="2">
+        <v>2</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="J30" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="2">
-        <v>1</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
       <c r="O30" s="2" t="s">
-        <v>153</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="F31" s="2" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
       <c r="O31" s="2" t="s">
-        <v>153</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>63</v>
+        <v>154</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H32" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
       <c r="O32" s="2" t="s">
-        <v>165</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>162</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H33" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
       <c r="O33" s="2" t="s">
-        <v>165</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>171</v>
-      </c>
       <c r="E34" s="2" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H34" s="2">
         <v>1</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
       <c r="O34" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H35" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="O35" s="2" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>183</v>
-      </c>
       <c r="E36" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H36" s="2">
         <v>1</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
       <c r="O36" s="2" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H37" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
       <c r="O37" s="2" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H38" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
       <c r="O38" s="2" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H39" s="2">
         <v>1</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
       <c r="O39" s="2" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
     </row>
     <row r="40" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>54</v>
+        <v>185</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H40" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>56</v>
+        <v>148</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
       <c r="O40" s="2" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
     </row>
     <row r="41" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>54</v>
+        <v>185</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H41" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
     </row>
     <row r="42" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H42" s="2">
         <v>1</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
       <c r="O42" s="2" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
     </row>
     <row r="43" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H43" s="2">
         <v>2</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
       <c r="O43" s="2" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
     </row>
     <row r="44" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H44" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>34</v>
+        <v>205</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
       <c r="O44" s="2" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
     </row>
     <row r="45" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H45" s="2">
         <v>1</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
       <c r="O45" s="2" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
     </row>
     <row r="46" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H46" s="2">
         <v>1</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
       <c r="O46" s="2" t="s">
-        <v>234</v>
+        <v>207</v>
       </c>
     </row>
     <row r="47" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H47" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2" t="s">
-        <v>241</v>
+        <v>207</v>
       </c>
     </row>
     <row r="48" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H48" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="2" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
     </row>
     <row r="49" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H49" s="2">
         <v>1</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
       <c r="O49" s="2" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="50" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>249</v>
+        <v>228</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H50" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
       <c r="O50" s="2" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>54</v>
+        <v>230</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H51" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
       <c r="O51" s="2" t="s">
-        <v>261</v>
+        <v>234</v>
       </c>
     </row>
     <row r="52" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>54</v>
+        <v>241</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H52" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>262</v>
+        <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>263</v>
+        <v>58</v>
       </c>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
       <c r="O52" s="2" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
     </row>
     <row r="53" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>264</v>
+        <v>239</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>265</v>
+        <v>240</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>267</v>
+        <v>242</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H53" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>268</v>
+        <v>244</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>269</v>
+        <v>38</v>
       </c>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
       <c r="O53" s="2" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
     </row>
     <row r="54" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>264</v>
+        <v>239</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>265</v>
+        <v>240</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>267</v>
+        <v>242</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H54" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>271</v>
+        <v>245</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>272</v>
+        <v>246</v>
       </c>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
       <c r="O54" s="2" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
     </row>
     <row r="55" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>273</v>
+        <v>239</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>274</v>
+        <v>240</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>275</v>
+        <v>241</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H55" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>278</v>
+        <v>248</v>
       </c>
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
       <c r="N55" s="2"/>
       <c r="O55" s="2" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
     </row>
     <row r="56" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>273</v>
+        <v>239</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>274</v>
+        <v>240</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>275</v>
+        <v>241</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H56" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>280</v>
+        <v>249</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>281</v>
+        <v>200</v>
       </c>
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
       <c r="O56" s="2" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
     </row>
     <row r="57" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>282</v>
+        <v>239</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>283</v>
+        <v>240</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>284</v>
+        <v>241</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>285</v>
+        <v>242</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H57" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>286</v>
+        <v>250</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
       <c r="O57" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H58" s="2">
+        <v>1</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
+      <c r="M58" s="2"/>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H59" s="2">
+        <v>2</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H60" s="2">
+        <v>3</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
+      <c r="M60" s="2"/>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H61" s="2">
+        <v>1</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
+      <c r="M61" s="2"/>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H62" s="2">
+        <v>2</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H63" s="2">
+        <v>3</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H64" s="2">
+        <v>1</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="K64" s="2"/>
+      <c r="L64" s="2"/>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H65" s="2">
+        <v>2</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H66" s="2">
+        <v>3</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K66" s="2"/>
+      <c r="L66" s="2"/>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H67" s="2">
+        <v>1</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
+      <c r="M67" s="2"/>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>288</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H68" s="2">
+        <v>1</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2" t="s">
+        <v>269</v>
       </c>
     </row>
   </sheetData>

--- a/reports/SCRUM-101/generated-testcases.xlsx
+++ b/reports/SCRUM-101/generated-testcases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="263">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -61,10 +61,13 @@
     <t>TC-001</t>
   </si>
   <si>
-    <t>Complete Checkout with a Single Item (End-to-End Happy Path)</t>
-  </si>
-  <si>
-    <t>FR1, FR3, FR4, FR5, FR6, FR8, FR9, FR10, FR11, FR12, FR13, FR14, FR15, FR20, AC1, AC2, AC3, AC4, BR4</t>
+    <t>Complete checkout with a single item (happy path)</t>
+  </si>
+  <si>
+    <t>FR1,FR3,FR4,FR5,FR8,FR9,FR10,FR11,FR12,FR13,FR14,FR15,FR20;AC1,AC2,AC3,AC4</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
   <si>
     <t>Critical</t>
@@ -73,712 +76,730 @@
     <t>Draft</t>
   </si>
   <si>
-    <t>Navigate to https://www.saucedemo.com and log in with standard_user / secret_sauce.</t>
-  </si>
-  <si>
-    <t>User is redirected to /inventory.html (Products page).</t>
-  </si>
-  <si>
-    <t>Smoke, Regression, Positive, E2E</t>
-  </si>
-  <si>
-    <t>Click 'Add to cart' for Sauce Labs Backpack.</t>
-  </si>
-  <si>
-    <t>Cart badge shows '1'; button changes to 'Remove'.</t>
-  </si>
-  <si>
-    <t>Click the cart icon to open the Cart page.</t>
-  </si>
-  <si>
-    <t>Cart page (cart.html) lists Sauce Labs Backpack with quantity 1, description, and price $29.99.</t>
-  </si>
-  <si>
-    <t>Click 'Checkout'.</t>
-  </si>
-  <si>
-    <t>User is redirected to /checkout-step-one.html ('Checkout: Your Information').</t>
-  </si>
-  <si>
-    <t>Enter First Name 'Jane', Last Name 'Smith', Zip '12345', click 'Continue'.</t>
-  </si>
-  <si>
-    <t>User is redirected to /checkout-step-two.html ('Checkout: Overview').</t>
-  </si>
-  <si>
-    <t>Review the Overview page.</t>
-  </si>
-  <si>
-    <t>Sauce Labs Backpack line item (qty 1, $29.99) shown; Payment Information 'SauceCard #31337'; Shipping Information 'Free Pony Express Delivery!'; Item total $29.99, Tax $2.40 (8%), Total $32.39.</t>
-  </si>
-  <si>
-    <t>Click 'Finish'.</t>
-  </si>
-  <si>
-    <t>User is redirected to /checkout-complete.html; heading 'Thank you for your order!' displayed; cart badge shows empty.</t>
-  </si>
-  <si>
-    <t>Click 'Back Home'.</t>
+    <t>Navigate to https://www.saucedemo.com and log in with standard_user / secret_sauce</t>
+  </si>
+  <si>
+    <t>User is redirected to /inventory.html (Products page)</t>
+  </si>
+  <si>
+    <t>Positive;Smoke;Regression</t>
+  </si>
+  <si>
+    <t>Click "Add to cart" for Sauce Labs Backpack</t>
+  </si>
+  <si>
+    <t>Cart badge shows "1"; button changes to "Remove"</t>
+  </si>
+  <si>
+    <t>Click the cart icon to open the Cart page</t>
+  </si>
+  <si>
+    <t>Cart page (cart.html) lists Sauce Labs Backpack with quantity 1, description, and price $29.99</t>
+  </si>
+  <si>
+    <t>Click "Checkout"</t>
+  </si>
+  <si>
+    <t>User is redirected to /checkout-step-one.html ("Checkout: Your Information")</t>
+  </si>
+  <si>
+    <t>Enter First Name "Jane", Last Name "Smith", Zip "12345", then click "Continue"</t>
+  </si>
+  <si>
+    <t>User is redirected to /checkout-step-two.html ("Checkout: Overview")</t>
+  </si>
+  <si>
+    <t>Review the Overview page</t>
+  </si>
+  <si>
+    <t>Sauce Labs Backpack line item (qty 1, $29.99) is shown; Payment Information "SauceCard #31337" is shown; Shipping Information "Free Pony Express Delivery!" is shown; Item total: $29.99, Tax: $2.40 (8%), Total: $32.39</t>
+  </si>
+  <si>
+    <t>Click "Finish"</t>
+  </si>
+  <si>
+    <t>User is redirected to /checkout-complete.html; heading "Thank you for your order!" is displayed; cart badge shows empty (no count)</t>
+  </si>
+  <si>
+    <t>Click "Back Home"</t>
   </si>
   <si>
     <t>TC-002</t>
   </si>
   <si>
-    <t>Complete Checkout with Multiple Items and Verify Price Arithmetic</t>
-  </si>
-  <si>
-    <t>FR1, FR9, FR11, AC1, AC3</t>
-  </si>
-  <si>
-    <t>Add Sauce Labs Backpack and Sauce Labs Bike Light to the cart.</t>
-  </si>
-  <si>
-    <t>Cart badge shows '2'.</t>
-  </si>
-  <si>
-    <t>Smoke, Regression, Positive, Calculation</t>
-  </si>
-  <si>
-    <t>Open the Cart page.</t>
-  </si>
-  <si>
-    <t>Both items are listed with quantity 1 each and correct individual prices.</t>
-  </si>
-  <si>
-    <t>Click 'Checkout', fill in valid First Name, Last Name, and Zip, click 'Continue'.</t>
-  </si>
-  <si>
-    <t>User reaches the Overview page listing both items.</t>
-  </si>
-  <si>
-    <t>Read the 'Item total', 'Tax', and 'Total' values on the Overview page.</t>
-  </si>
-  <si>
-    <t>Item total = $39.98 (29.99 + 9.99); Tax = $3.20 (8% of $39.98, rounded); Total = $43.18.</t>
-  </si>
-  <si>
-    <t>Order completes successfully and cart is cleared.</t>
+    <t>Complete checkout with multiple items and verify price arithmetic</t>
+  </si>
+  <si>
+    <t>FR1,FR8,FR9,FR11,FR13,FR20;AC1,AC3,AC4</t>
+  </si>
+  <si>
+    <t>Log in as standard_user; add Sauce Labs Backpack ($29.99) and Sauce Labs Bike Light ($9.99) to the cart</t>
+  </si>
+  <si>
+    <t>Cart badge shows "2"</t>
+  </si>
+  <si>
+    <t>Open the Cart page</t>
+  </si>
+  <si>
+    <t>Both items are listed with quantity 1 each and correct individual prices</t>
+  </si>
+  <si>
+    <t>Click "Checkout", fill in valid First Name, Last Name, and Zip, then click "Continue"</t>
+  </si>
+  <si>
+    <t>User reaches the Overview page listing both items</t>
+  </si>
+  <si>
+    <t>Read the "Item total", "Tax", and "Total" values on the Overview page</t>
+  </si>
+  <si>
+    <t>Item total = $39.98 (29.99 + 9.99); Tax = $3.20 (8% of $39.98, rounded); Total = $43.18 (Item total + Tax)</t>
+  </si>
+  <si>
+    <t>Order completes successfully; cart is cleared</t>
   </si>
   <si>
     <t>TC-003</t>
   </si>
   <si>
-    <t>Cart Page Displays Full Item Details for Each Product</t>
-  </si>
-  <si>
-    <t>FR1, AC1</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Major</t>
-  </si>
-  <si>
-    <t>Item name 'Sauce Labs Backpack' is visible; item description text is visible; item price '$29.99' is visible; item quantity '1' is visible.</t>
-  </si>
-  <si>
-    <t>Functional, Positive</t>
+    <t>Cart page displays full item details for each product</t>
+  </si>
+  <si>
+    <t>FR1;AC1</t>
+  </si>
+  <si>
+    <t>Log in as standard_user and add Sauce Labs Backpack to the cart</t>
+  </si>
+  <si>
+    <t>Item added; cart badge shows "1"</t>
+  </si>
+  <si>
+    <t>Positive;CartReview</t>
+  </si>
+  <si>
+    <t>Item name "Sauce Labs Backpack" is visible; item description text is visible; item price "$29.99" is visible; item quantity "1" is visible</t>
   </si>
   <si>
     <t>TC-004</t>
   </si>
   <si>
-    <t>Cart Page Offers Continue Shopping and Checkout Options</t>
-  </si>
-  <si>
-    <t>FR3, AC1</t>
-  </si>
-  <si>
-    <t>Verify 'Continue Shopping' and 'Checkout' buttons on the Cart page.</t>
-  </si>
-  <si>
-    <t>Both buttons are visible and enabled.</t>
-  </si>
-  <si>
-    <t>Functional, Positive, Navigation</t>
-  </si>
-  <si>
-    <t>Click 'Continue Shopping'.</t>
-  </si>
-  <si>
-    <t>User is redirected to /inventory.html; cart badge count is unchanged (item still in cart).</t>
+    <t>Cart page offers Continue Shopping and Checkout options</t>
+  </si>
+  <si>
+    <t>FR3;AC1</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Log in as standard_user, add any item, and open the Cart page</t>
+  </si>
+  <si>
+    <t>"Continue Shopping" button is visible and enabled; "Checkout" button is visible and enabled</t>
+  </si>
+  <si>
+    <t>Click "Continue Shopping"</t>
+  </si>
+  <si>
+    <t>User is redirected to /inventory.html; cart badge count is unchanged (item still in cart)</t>
   </si>
   <si>
     <t>TC-005</t>
   </si>
   <si>
-    <t>[DEFECT] Cart Page Does Not Display a Total/Subtotal Price</t>
-  </si>
-  <si>
-    <t>FR2, AC1</t>
-  </si>
-  <si>
-    <t>2.3 (DISCREPANCY)</t>
-  </si>
-  <si>
-    <t>Blocked - Known Defect</t>
-  </si>
-  <si>
-    <t>Open the Cart page and inspect for any subtotal/tax/total price element.</t>
-  </si>
-  <si>
-    <t>The Cart page displays the total price calculation for all items in the cart (FR2, AC1).</t>
-  </si>
-  <si>
-    <t>No subtotal, tax, or total price element is present anywhere on cart.html - only the two individual item prices are shown. Total/subtotal/tax only appear later, on the Overview page.</t>
-  </si>
-  <si>
-    <t>Fail - Confirmed Defect</t>
-  </si>
-  <si>
-    <t>Negative, Defect, Requirement-Gap</t>
+    <t>DISCREPANCY: Cart page does not display a total/subtotal price</t>
+  </si>
+  <si>
+    <t>FR2;AC1</t>
+  </si>
+  <si>
+    <t>Log in as standard_user, add two items with different prices, and open the Cart page</t>
+  </si>
+  <si>
+    <t>Per Requirement (Expected): Per FR2/AC1, the Cart page should display the total price calculation for the items in the cart. Observed (Live Application): No subtotal, tax, or total price element is present anywhere on cart.html — only the two individual item prices are shown. Confirmed requirement-vs-implementation gap (FR2), flagged for AI Failure Classification / defect triage.</t>
+  </si>
+  <si>
+    <t>Discrepancy;Defect-Candidate;CartReview</t>
   </si>
   <si>
     <t>TC-006</t>
   </si>
   <si>
-    <t>Submitting an Entirely Empty Form Shows First Name Required Error First</t>
-  </si>
-  <si>
-    <t>FR5, FR6, FR7, AC2, BR1</t>
-  </si>
-  <si>
-    <t>Verify First Name, Last Name, and Zip/Postal Code fields are present, leave all three empty, click 'Continue'.</t>
-  </si>
-  <si>
-    <t>Fields for First Name, Last Name, and Zip/Postal Code are displayed (FR5). An error alert is shown reading 'Error: First Name is required'; user remains on checkout-step-one.html.</t>
-  </si>
-  <si>
-    <t>Negative, Validation</t>
+    <t>Submitting an entirely empty form shows First Name required error first</t>
+  </si>
+  <si>
+    <t>FR6,FR7;AC2;BR1</t>
+  </si>
+  <si>
+    <t>Log in as standard_user, add an item, open Cart, click "Checkout" to reach checkout-step-one.html</t>
+  </si>
+  <si>
+    <t>User is on the Checkout: Your Information page</t>
+  </si>
+  <si>
+    <t>Negative;Validation</t>
+  </si>
+  <si>
+    <t>Leave all three fields empty and click "Continue"</t>
+  </si>
+  <si>
+    <t>An error alert is shown reading "Error: First Name is required"; user remains on checkout-step-one.html</t>
   </si>
   <si>
     <t>TC-007</t>
   </si>
   <si>
-    <t>Leaving Only Last Name Empty Shows Last Name Required Error</t>
-  </si>
-  <si>
-    <t>FR6, FR7, AC2, BR1</t>
-  </si>
-  <si>
-    <t>Enter First Name only, leave Last Name and Zip empty, click 'Continue'.</t>
-  </si>
-  <si>
-    <t>Error alert reads 'Error: Last Name is required'; user remains on checkout-step-one.html.</t>
+    <t>Leaving only Last Name empty shows Last Name required error</t>
+  </si>
+  <si>
+    <t>Enter First Name only, leave Last Name and Zip empty, click "Continue"</t>
+  </si>
+  <si>
+    <t>Error alert reads "Error: Last Name is required"; user remains on checkout-step-one.html</t>
   </si>
   <si>
     <t>TC-008</t>
   </si>
   <si>
-    <t>Leaving Only Zip/Postal Code Empty Shows Postal Code Required Error</t>
-  </si>
-  <si>
-    <t>Enter First Name and Last Name, leave Zip empty, click 'Continue'.</t>
-  </si>
-  <si>
-    <t>Error alert reads 'Error: Postal Code is required'; user remains on checkout-step-one.html.</t>
+    <t>Leaving only Zip/Postal Code empty shows Postal Code required error</t>
+  </si>
+  <si>
+    <t>Enter First Name and Last Name, leave Zip empty, click "Continue"</t>
+  </si>
+  <si>
+    <t>Error alert reads "Error: Postal Code is required"; user remains on checkout-step-one.html</t>
   </si>
   <si>
     <t>TC-009</t>
   </si>
   <si>
-    <t>Valid First Name, Last Name, and Zip Proceed to Overview Page</t>
-  </si>
-  <si>
-    <t>FR4, FR8, AC2, AC3</t>
-  </si>
-  <si>
-    <t>User is redirected to /checkout-step-two.html with no error alert shown.</t>
-  </si>
-  <si>
-    <t>Positive, Gating</t>
+    <t>Valid First Name, Last Name, and Zip proceed to Overview page</t>
+  </si>
+  <si>
+    <t>FR4,FR5,FR6,FR8;AC2,AC3</t>
+  </si>
+  <si>
+    <t>Enter First Name "Jane", Last Name "Smith", Zip "12345", click "Continue"</t>
+  </si>
+  <si>
+    <t>User is redirected to /checkout-step-two.html; no error alert is shown</t>
+  </si>
+  <si>
+    <t>Positive;Validation</t>
   </si>
   <si>
     <t>TC-010</t>
   </si>
   <si>
-    <t>Error Alert Can Be Dismissed via Its Close Control</t>
-  </si>
-  <si>
-    <t>FR7, NFR4</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Minor</t>
-  </si>
-  <si>
-    <t>Click 'Continue' with all fields empty to trigger the required-field error.</t>
-  </si>
-  <si>
-    <t>Error alert is visible.</t>
-  </si>
-  <si>
-    <t>UI, Usability</t>
-  </si>
-  <si>
-    <t>Click the 'Dismiss error' (X) control on the alert.</t>
-  </si>
-  <si>
-    <t>The error alert is no longer visible; form fields remain empty and editable.</t>
+    <t>Error alert can be dismissed via its close control</t>
+  </si>
+  <si>
+    <t>FR7;NFR4</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Click "Continue" with all fields empty to trigger the required-field error</t>
+  </si>
+  <si>
+    <t>Error alert is visible</t>
+  </si>
+  <si>
+    <t>Positive;UX</t>
+  </si>
+  <si>
+    <t>Click the "Dismiss error" (X) control on the alert</t>
+  </si>
+  <si>
+    <t>The error alert is no longer visible; the form fields remain empty and editable</t>
   </si>
   <si>
     <t>TC-011</t>
   </si>
   <si>
-    <t>[DEFECT] Special Characters in Zip/Postal Code Are Accepted Without a Format Validation Error</t>
-  </si>
-  <si>
-    <t>AC5, FR16, FR17</t>
-  </si>
-  <si>
-    <t>3.6 (DISCREPANCY)</t>
-  </si>
-  <si>
-    <t>Enter First Name 'John', Last Name 'Doe', Zip '!@#$%', click 'Continue'.</t>
-  </si>
-  <si>
-    <t>A format-validation error is shown for the invalid Zip value; user cannot proceed until it is corrected (AC5, FR16, FR17).</t>
-  </si>
-  <si>
-    <t>No format-validation error is shown; user is redirected to /checkout-step-two.html despite the non-numeric, special-character Zip value.</t>
-  </si>
-  <si>
-    <t>Negative, Defect, Boundary</t>
+    <t>DISCREPANCY: Special characters in Zip/Postal Code accepted without format validation error</t>
+  </si>
+  <si>
+    <t>FR16,FR17;AC5</t>
+  </si>
+  <si>
+    <t>Enter First Name "John", Last Name "Doe", Zip "!@#$%", click "Continue"</t>
+  </si>
+  <si>
+    <t>Per Requirement (Expected): Per AC5/FR16/FR17, entering invalid data such as special characters should produce a validation error message and block progression. Observed (Live Application): No format-validation error is shown; user is redirected to /checkout-step-two.html despite the non-numeric, special-character Zip value. Confirmed defect against AC5/FR16/FR17.</t>
+  </si>
+  <si>
+    <t>Discrepancy;Defect-Candidate;Validation</t>
   </si>
   <si>
     <t>TC-012</t>
   </si>
   <si>
-    <t>[DEFECT] Whitespace-Only First Name Is Accepted as Valid</t>
-  </si>
-  <si>
-    <t>FR6, FR7, AC5</t>
-  </si>
-  <si>
-    <t>3.7 (DISCREPANCY)</t>
-  </si>
-  <si>
-    <t>Enter First Name as three spaces '   ', Last Name 'Doe', Zip '12345', click 'Continue'.</t>
-  </si>
-  <si>
-    <t>A 'First Name is required' error is shown, since the field is effectively blank (FR6/FR7; AC5 rejects incomplete information).</t>
-  </si>
-  <si>
-    <t>No 'First Name is required' error is shown; user is redirected to /checkout-step-two.html.</t>
-  </si>
-  <si>
-    <t>Negative, Defect</t>
+    <t>DISCREPANCY: Whitespace-only First Name accepted as valid</t>
+  </si>
+  <si>
+    <t>FR6,FR16,FR17;AC5</t>
+  </si>
+  <si>
+    <t>Enter First Name as three spaces ("   "), Last Name "Doe", Zip "12345", click "Continue"</t>
+  </si>
+  <si>
+    <t>Per Requirement (Expected): Per FR6/FR7 (mandatory field enforcement) and AC5 (incomplete information should be rejected), a whitespace-only First Name should be treated as effectively empty and trigger the "First Name is required" error. Observed (Live Application): No "First Name is required" error is shown even though the field is effectively blank; user is redirected to /checkout-step-two.html. Confirmed defect against FR6/FR7/AC5.</t>
   </si>
   <si>
     <t>TC-013</t>
   </si>
   <si>
-    <t>[DEFECT] Oversized Name Input and Special-Character Last Name Are Both Accepted</t>
-  </si>
-  <si>
-    <t>3.8 (DISCREPANCY)</t>
-  </si>
-  <si>
-    <t>Enter a First Name of 90+ characters, a Last Name containing digits and special characters ('Doe123!@#'), and a valid Zip, click 'Continue'.</t>
-  </si>
-  <si>
-    <t>A length-limit or character-format error is shown for one or both fields (AC5, FR16, FR17).</t>
-  </si>
-  <si>
-    <t>No length-limit or character-format error is shown for either field; user is redirected to /checkout-step-two.html.</t>
+    <t>DISCREPANCY: Oversized name input and special-character Last Name both accepted</t>
+  </si>
+  <si>
+    <t>Enter a First Name of 90+ characters, a Last Name containing digits and special characters ("Doe123!@#"), and a valid Zip, then click "Continue"</t>
+  </si>
+  <si>
+    <t>Per Requirement (Expected): Per AC5/FR16/FR17, oversized or malformed name input should trigger a length-limit or character-format validation error. Observed (Live Application): No length-limit or character-format error is shown for either field; user is redirected to /checkout-step-two.html. Confirms no max-length or allowed-character validation exists, contradicting the intent of AC5/FR16/FR17.</t>
   </si>
   <si>
     <t>TC-014</t>
   </si>
   <si>
-    <t>Numeric 5-Digit Zip/Postal Code Is Accepted (Happy-Path Boundary)</t>
-  </si>
-  <si>
-    <t>AC2</t>
-  </si>
-  <si>
-    <t>Enter valid First Name and Last Name, enter Zip '99999', click 'Continue'.</t>
-  </si>
-  <si>
-    <t>User is redirected to /checkout-step-two.html with no errors.</t>
-  </si>
-  <si>
-    <t>Positive, Boundary</t>
+    <t>Numeric 5-digit Zip/Postal Code is accepted (happy-path boundary)</t>
+  </si>
+  <si>
+    <t>FR5,FR8;AC2</t>
+  </si>
+  <si>
+    <t>Enter valid First Name and Last Name, enter Zip "99999", click "Continue"</t>
+  </si>
+  <si>
+    <t>User is redirected to /checkout-step-two.html with no errors</t>
+  </si>
+  <si>
+    <t>Positive;Boundary;Validation</t>
   </si>
   <si>
     <t>TC-015</t>
   </si>
   <si>
-    <t>Overview Page Lists All Cart Items with Correct Details</t>
-  </si>
-  <si>
-    <t>FR9, FR11, AC3</t>
-  </si>
-  <si>
-    <t>Review the Overview page item list.</t>
-  </si>
-  <si>
-    <t>Both items are listed with correct name, quantity (1 each), and price; no 'Add to cart' / 'Remove' controls are shown on this read-only summary.</t>
+    <t>Overview page lists all cart items with correct details</t>
+  </si>
+  <si>
+    <t>FR9;AC3</t>
+  </si>
+  <si>
+    <t>Log in, add Sauce Labs Backpack and Sauce Labs Bike Light to the cart, and proceed through checkout information with valid data to reach checkout-step-two.html</t>
+  </si>
+  <si>
+    <t>Both items are listed with correct name, quantity (1 each), and price; no "Add to cart" / "Remove" controls are shown on this read-only summary</t>
+  </si>
+  <si>
+    <t>Positive;Overview</t>
   </si>
   <si>
     <t>TC-016</t>
   </si>
   <si>
-    <t>Overview Page Displays Payment and Shipping Information Sections</t>
-  </si>
-  <si>
-    <t>FR10, AC3</t>
-  </si>
-  <si>
-    <t>Inspect the Payment Information and Shipping Information sections.</t>
-  </si>
-  <si>
-    <t>'Payment Information:' section shows 'SauceCard #31337'; 'Shipping Information:' section shows 'Free Pony Express Delivery!'.</t>
+    <t>Overview page displays Payment and Shipping information sections</t>
+  </si>
+  <si>
+    <t>FR10;AC3</t>
+  </si>
+  <si>
+    <t>Reach checkout-step-two.html with at least one item in the cart</t>
+  </si>
+  <si>
+    <t>"Payment Information:" section shows "SauceCard #31337"; "Shipping Information:" section shows "Free Pony Express Delivery!"</t>
   </si>
   <si>
     <t>TC-017</t>
   </si>
   <si>
-    <t>Overview Page Provides Cancel and Finish Controls</t>
-  </si>
-  <si>
-    <t>FR12, AC3</t>
-  </si>
-  <si>
-    <t>Verify the Overview page controls.</t>
-  </si>
-  <si>
-    <t>'Cancel' button is visible and enabled; 'Finish' button is visible and enabled.</t>
+    <t>Overview page provides Cancel and Finish controls</t>
+  </si>
+  <si>
+    <t>FR12;AC3</t>
+  </si>
+  <si>
+    <t>"Cancel" button is visible and enabled; "Finish" button is visible and enabled</t>
   </si>
   <si>
     <t>TC-018</t>
   </si>
   <si>
-    <t>Finish Redirects to Confirmation Page with Success Message</t>
-  </si>
-  <si>
-    <t>FR13, FR14, AC4</t>
-  </si>
-  <si>
-    <t>User is redirected to /checkout-complete.html; heading 'Thank you for your order!' is displayed; descriptive dispatch/delivery text is displayed; 'Back Home' button is visible.</t>
-  </si>
-  <si>
-    <t>Positive, Smoke</t>
+    <t>Finish redirects to confirmation page with success message</t>
+  </si>
+  <si>
+    <t>FR13,FR14,FR15;AC4</t>
+  </si>
+  <si>
+    <t>Complete checkout information and reach checkout-step-two.html with at least one item, then click "Finish"</t>
+  </si>
+  <si>
+    <t>User is redirected to /checkout-complete.html; heading "Thank you for your order!" is displayed; descriptive text about dispatch/delivery is displayed; "Back Home" button is visible</t>
+  </si>
+  <si>
+    <t>Positive;OrderCompletion</t>
   </si>
   <si>
     <t>TC-019</t>
   </si>
   <si>
-    <t>Back Home Button Returns to the Products Page</t>
-  </si>
-  <si>
-    <t>FR15, AC4</t>
-  </si>
-  <si>
-    <t>User is redirected to /inventory.html (Products page); product grid is displayed.</t>
-  </si>
-  <si>
-    <t>Positive, Navigation</t>
+    <t>Back Home button returns to the Products page</t>
+  </si>
+  <si>
+    <t>FR15;AC4</t>
+  </si>
+  <si>
+    <t>Reach checkout-complete.html by completing an order</t>
+  </si>
+  <si>
+    <t>Confirmation page is displayed</t>
+  </si>
+  <si>
+    <t>User is redirected to /inventory.html (Products page); product grid is displayed</t>
   </si>
   <si>
     <t>TC-020</t>
   </si>
   <si>
-    <t>Cart Is Cleared After Order Confirmation</t>
-  </si>
-  <si>
-    <t>FR20, BR4</t>
-  </si>
-  <si>
-    <t>Add two items to the cart, complete checkout through 'Finish' to reach checkout-complete.html.</t>
-  </si>
-  <si>
-    <t>Cart icon shows no item count badge ('Cart, empty').</t>
-  </si>
-  <si>
-    <t>Positive, Data-Integrity</t>
-  </si>
-  <si>
-    <t>Open the Cart page directly.</t>
-  </si>
-  <si>
-    <t>Cart page shows zero line items.</t>
+    <t>Cart is cleared after order confirmation</t>
+  </si>
+  <si>
+    <t>FR20;BR4</t>
+  </si>
+  <si>
+    <t>Add two items to the cart, complete checkout through "Finish" to reach checkout-complete.html</t>
+  </si>
+  <si>
+    <t>Cart icon shows no item count badge ("Cart, empty")</t>
+  </si>
+  <si>
+    <t>Open the Cart page directly</t>
+  </si>
+  <si>
+    <t>Cart page shows zero line items</t>
   </si>
   <si>
     <t>TC-021</t>
   </si>
   <si>
-    <t>Unauthenticated Direct Access to Checkout Is Blocked and Redirected to Login</t>
-  </si>
-  <si>
-    <t>FR18, BR2</t>
-  </si>
-  <si>
-    <t>Without logging in (or after explicitly logging out), navigate directly to https://www.saucedemo.com/checkout-step-one.html.</t>
-  </si>
-  <si>
-    <t>User is redirected to the login page ('/'); an error alert is shown reading: "Epic sadface: You can only access '/checkout-step-one.html' when you are logged in."</t>
-  </si>
-  <si>
-    <t>Security, Access-Control, Negative</t>
+    <t>Unauthenticated direct access to checkout is blocked and redirected to login</t>
+  </si>
+  <si>
+    <t>FR18;BR2</t>
+  </si>
+  <si>
+    <t>Without logging in (or after explicitly logging out), navigate directly to https://www.saucedemo.com/checkout-step-one.html</t>
+  </si>
+  <si>
+    <t>User is redirected to the login page ("/"); an error alert is shown reading: "Epic sadface: You can only access '/checkout-step-one.html' when you are logged in."</t>
+  </si>
+  <si>
+    <t>Negative;Security;AccessControl</t>
   </si>
   <si>
     <t>TC-022</t>
   </si>
   <si>
-    <t>[DEFECT] Checking Out with an Empty Cart Is Not Blocked and Can Be Completed with a $0.00 Total</t>
-  </si>
-  <si>
-    <t>FR19, BR3</t>
-  </si>
-  <si>
-    <t>6.2 (DISCREPANCY)</t>
-  </si>
-  <si>
-    <t>Open the Cart page with zero items.</t>
-  </si>
-  <si>
-    <t>'Checkout' should be disabled, hidden, or otherwise prevent proceeding when the cart is empty (BR3, FR19).</t>
-  </si>
-  <si>
-    <t>'Checkout' button is present and enabled even though the cart has zero items.</t>
-  </si>
-  <si>
-    <t>Negative, Defect, Business-Rule, Data-Integrity</t>
-  </si>
-  <si>
-    <t>User should be blocked from reaching checkout-step-one.html, or shown an empty-cart message.</t>
-  </si>
-  <si>
-    <t>User is unexpectedly redirected to /checkout-step-one.html.</t>
-  </si>
-  <si>
-    <t>Fill in valid First Name, Last Name, and Zip, then click 'Continue'.</t>
-  </si>
-  <si>
-    <t>This step should be unreachable per BR3/FR19.</t>
-  </si>
-  <si>
-    <t>User reaches /checkout-step-two.html showing 'Item total: $0', 'Tax: $0.00', 'Total: $0.00', and no line items.</t>
-  </si>
-  <si>
-    <t>An order with zero items should not be completable.</t>
-  </si>
-  <si>
-    <t>Order completes successfully and /checkout-complete.html is shown, confirming an order with zero items was allowed end-to-end.</t>
+    <t>DISCREPANCY: Checking out with an empty cart is not blocked and can be completed with a $0.00 total</t>
+  </si>
+  <si>
+    <t>FR19;BR3</t>
+  </si>
+  <si>
+    <t>Log in as standard_user with a guaranteed-empty cart, open the Cart page</t>
+  </si>
+  <si>
+    <t>Per Requirement (Expected): Per BR3/FR19, the "Checkout" button should not be present, should be disabled, or should be blocked with an empty-cart message when the cart has zero items. Observed (Live Application): "Checkout" button is present and enabled even though the cart has zero items.</t>
+  </si>
+  <si>
+    <t>Discrepancy;Defect-Candidate;BusinessRule</t>
+  </si>
+  <si>
+    <t>Per Requirement (Expected): User should be blocked from proceeding. Observed (Live Application): User is unexpectedly redirected to /checkout-step-one.html.</t>
+  </si>
+  <si>
+    <t>Fill in valid First Name, Last Name, and Zip, then click "Continue"</t>
+  </si>
+  <si>
+    <t>Observed (Live Application): User reaches /checkout-step-two.html showing "Item total: $0", "Tax: $0.00", "Total: $0.00", and no line items.</t>
+  </si>
+  <si>
+    <t>Per Requirement (Expected): An order with zero items should never be able to complete, per BR3/FR19. Observed (Live Application): Order completes successfully and /checkout-complete.html is shown, confirming an order with zero items was allowed end-to-end. Confirmed defect against BR3/FR19 — flag for downstream AI Failure Classification as an application/business-logic defect.</t>
   </si>
   <si>
     <t>TC-023</t>
   </si>
   <si>
-    <t>Logged-In Session Persists Across Checkout Steps for a Valid Multi-Step Flow</t>
-  </si>
-  <si>
-    <t>BR2</t>
-  </si>
-  <si>
-    <t>Add an item, and progress through Cart -&gt; Checkout Info -&gt; Overview -&gt; Complete without logging out.</t>
-  </si>
-  <si>
-    <t>No re-authentication is required at any step; each page transition succeeds without redirect to login.</t>
-  </si>
-  <si>
-    <t>Positive, Session</t>
+    <t>Logged-in session persists across checkout steps for a valid multi-step flow</t>
+  </si>
+  <si>
+    <t>Log in as standard_user, add an item, and progress through Cart -&gt; Checkout Info -&gt; Overview -&gt; Complete without logging out</t>
+  </si>
+  <si>
+    <t>No re-authentication is required at any step; each page transition succeeds without redirect to login</t>
+  </si>
+  <si>
+    <t>Positive;Session</t>
   </si>
   <si>
     <t>TC-024</t>
   </si>
   <si>
-    <t>[DEFECT] Attempting to Check Out Again Immediately After Order Completion Reproduces the Same Empty-Cart Defect</t>
-  </si>
-  <si>
-    <t>6.4 (DISCREPANCY)</t>
-  </si>
-  <si>
-    <t>From the now-empty cart page, click 'Checkout' again.</t>
-  </si>
-  <si>
-    <t>The application should block checkout or show a 'cart is empty' guard message (BR3, FR19).</t>
-  </si>
-  <si>
-    <t>The application again allows navigation to checkout-step-one.html despite zero items, reproducing the BR3/FR19 gap rather than showing any guard message.</t>
-  </si>
-  <si>
-    <t>Fail - Confirmed Defect (repeatable)</t>
-  </si>
-  <si>
-    <t>Negative, Defect, Regression, Business-Rule</t>
+    <t>DISCREPANCY: Attempting to check out again immediately after order completion reproduces the empty-cart defect</t>
+  </si>
+  <si>
+    <t>Complete a full order for one item so the cart becomes empty, then click "Checkout" again from the now-empty cart page</t>
+  </si>
+  <si>
+    <t>Per Requirement (Expected): Per BR3/FR19, the application should show a "cart is empty" guard message and prevent navigation to checkout-step-one.html. Observed (Live Application): The application again allows navigation to checkout-step-one.html despite zero items, reproducing the BR3/FR19 gap rather than showing any guard message.</t>
   </si>
   <si>
     <t>TC-025</t>
   </si>
   <si>
-    <t>Cancel from Checkout Information Page Returns to Cart Page with Items Preserved</t>
-  </si>
-  <si>
-    <t>FR21, BR5</t>
-  </si>
-  <si>
-    <t>Click 'Cancel' on the Checkout Information page.</t>
-  </si>
-  <si>
-    <t>User is redirected to /cart.html (Your Cart); both items are still present in the cart with correct quantities and prices.</t>
+    <t>Cancel from Checkout Information page returns to Cart page with items preserved</t>
+  </si>
+  <si>
+    <t>FR21;BR5;OQ2 (resolved)</t>
+  </si>
+  <si>
+    <t>Log in, add two items to the cart, click "Checkout" to reach checkout-step-one.html</t>
+  </si>
+  <si>
+    <t>Positive;Navigation;Cancel</t>
+  </si>
+  <si>
+    <t>Click "Cancel" on the Checkout Information page</t>
+  </si>
+  <si>
+    <t>User is redirected to /cart.html (Your Cart); both items are still present in the cart with correct quantities and prices</t>
   </si>
   <si>
     <t>TC-026</t>
   </si>
   <si>
-    <t>[DEFECT] Cancel from Checkout Overview Page Returns to Products Page, Not the Cart Page</t>
-  </si>
-  <si>
-    <t>7.2 (DISCREPANCY)</t>
-  </si>
-  <si>
-    <t>Click 'Cancel' on the Checkout Overview page.</t>
-  </si>
-  <si>
-    <t>User is redirected to /cart.html, consistent with the step-one Cancel destination and the 'return to cart' intent implied by BR5.</t>
-  </si>
-  <si>
-    <t>User is redirected to /inventory.html (Products page), NOT /cart.html. Cart badge still shows the original item count, confirming cart contents are preserved even though the landing page differs.</t>
-  </si>
-  <si>
-    <t>Negative, Defect, Navigation, UX</t>
+    <t>DISCREPANCY: Cancel from Checkout Overview page returns to Products page, not the Cart page</t>
+  </si>
+  <si>
+    <t>FR21;BR5</t>
+  </si>
+  <si>
+    <t>Log in, add two items to the cart, proceed through valid checkout information to reach checkout-step-two.html</t>
+  </si>
+  <si>
+    <t>User is on the Checkout: Overview page</t>
+  </si>
+  <si>
+    <t>Discrepancy;Defect-Candidate;Navigation;Cancel</t>
+  </si>
+  <si>
+    <t>Click "Cancel" on the Checkout Overview page</t>
+  </si>
+  <si>
+    <t>Per Requirement (Expected): Per BR5's "return to cart" intent (and for consistency with the step-one Cancel behavior in TC-025), Cancel should return the user to /cart.html. Observed (Live Application): User is redirected to /inventory.html (Products page), NOT /cart.html — inconsistent with the step-one Cancel destination. Cart badge still shows the original item count, confirming cart contents are preserved even though the landing page differs. Confirmed inconsistency against BR5, flagged for defect triage.</t>
   </si>
   <si>
     <t>TC-027</t>
   </si>
   <si>
-    <t>Browser Back Button After Order Confirmation Shows a Stale Overview Page Whose Finish Button Is Still Clickable</t>
-  </si>
-  <si>
-    <t>OQ6</t>
-  </si>
-  <si>
-    <t>Draft - Known Issue</t>
-  </si>
-  <si>
-    <t>Click the browser Back button.</t>
-  </si>
-  <si>
-    <t>Browser navigates to /checkout-step-two.html showing an empty/zero-value order summary (cart already cleared); 'Finish' button is still present and enabled.</t>
-  </si>
-  <si>
-    <t>Negative, Known-Issue, Navigation</t>
-  </si>
-  <si>
-    <t>Click 'Finish' again.</t>
-  </si>
-  <si>
-    <t>User is redirected back to /checkout-complete.html without any error, confirming no safeguard exists against re-submitting/re-visiting a completed order via back navigation. Record as a known issue for defect triage - no documented requirement defines correct behavior here (OQ6).</t>
+    <t>DISCREPANCY: Browser back button after order confirmation shows a stale Overview page whose Finish button is still clickable</t>
+  </si>
+  <si>
+    <t>FR20;BR4;OQ6</t>
+  </si>
+  <si>
+    <t>Complete a full order for one item to reach checkout-complete.html</t>
+  </si>
+  <si>
+    <t>Discrepancy;Defect-Candidate;Navigation</t>
+  </si>
+  <si>
+    <t>Click the browser Back button</t>
+  </si>
+  <si>
+    <t>Per Requirement (Expected): No documented expectation exists for this action (OQ6 was open); at minimum BR4 implies the cart should remain cleared and no further order actions should be possible without re-adding items. Observed (Live Application): Browser navigates to /checkout-step-two.html showing an empty/zero-value order summary (cart already cleared); "Finish" button is still present and enabled.</t>
+  </si>
+  <si>
+    <t>Click "Finish" again</t>
+  </si>
+  <si>
+    <t>Observed (Live Application): User is redirected back to /checkout-complete.html without any error, confirming no safeguard exists against re-submitting/re-visiting a completed order via back navigation. Flagged as a defect-candidate for triage given the absence of a resubmission guard.</t>
   </si>
   <si>
     <t>TC-028</t>
   </si>
   <si>
-    <t>Full Checkout Flow Renders and Completes at a Mobile Viewport (375x667)</t>
+    <t>Full checkout flow renders and completes at a mobile viewport (375x667)</t>
   </si>
   <si>
     <t>NFR2</t>
   </si>
   <si>
-    <t>Set the browser viewport to 375x667 and log in as standard_user.</t>
-  </si>
-  <si>
-    <t>Login form and hamburger menu icon render without horizontal overflow.</t>
-  </si>
-  <si>
-    <t>Responsive, Mobile, Compatibility</t>
-  </si>
-  <si>
-    <t>Add an item to the cart and proceed through Cart -&gt; Checkout Info -&gt; Overview -&gt; Complete at this viewport.</t>
-  </si>
-  <si>
-    <t>All buttons and form fields remain visible, tappable, and functional at each step; no layout element is clipped or overlapping such that a user could not complete checkout.</t>
+    <t>Set the browser viewport to 375x667, log in as standard_user</t>
+  </si>
+  <si>
+    <t>Login form and hamburger menu icon render without horizontal overflow</t>
+  </si>
+  <si>
+    <t>NonFunctional;Mobile</t>
+  </si>
+  <si>
+    <t>Add an item to the cart and proceed through Cart -&gt; Checkout Info -&gt; Overview -&gt; Complete at this viewport</t>
+  </si>
+  <si>
+    <t>All buttons and form fields remain visible, tappable, and functional at each step; no layout element is clipped or overlapping such that a user could not complete checkout</t>
   </si>
   <si>
     <t>TC-029</t>
   </si>
   <si>
-    <t>All Checkout-Flow Validation and Success Messages Are Captured for Content Review</t>
-  </si>
-  <si>
-    <t>NFR5</t>
-  </si>
-  <si>
-    <t>Trigger each of: First Name required, Last Name required, Postal Code required, and the order-confirmation success message, capturing the exact text of each.</t>
-  </si>
-  <si>
-    <t>Messages match verbatim: 'Error: First Name is required'; 'Error: Last Name is required'; 'Error: Postal Code is required'; 'Thank you for your order!' success heading on checkout-complete.html. All messages recorded verbatim per NFR5.</t>
-  </si>
-  <si>
-    <t>Content, Documentation, Regression</t>
+    <t>All checkout-flow validation and success messages are captured verbatim for content review</t>
+  </si>
+  <si>
+    <t>NFR5;FR7;FR14</t>
+  </si>
+  <si>
+    <t>Trigger each of: First Name required, Last Name required, Postal Code required, and the order-confirmation success message, capturing the exact text of each</t>
+  </si>
+  <si>
+    <t>Message text is exactly: "Error: First Name is required"; "Error: Last Name is required"; "Error: Postal Code is required"; "Thank you for your order!" success heading on checkout-complete.html. All messages are recorded verbatim in test evidence per NFR5.</t>
+  </si>
+  <si>
+    <t>NonFunctional;ContentReview</t>
   </si>
   <si>
     <t>TC-030</t>
   </si>
   <si>
-    <t>[SUPPLEMENTAL] Cross-Browser Execution of the Smoke Checkout Flow</t>
+    <t>DISCREPANCY: Undocumented "Generate PDF order" button appears on the confirmation page</t>
+  </si>
+  <si>
+    <t>None (undocumented feature)</t>
+  </si>
+  <si>
+    <t>Plan Discrepancy Note #7 (Intro)</t>
+  </si>
+  <si>
+    <t>Per Requirement (Expected): Per AC4/FR13–FR15, only a "Back Home" button is documented on the confirmation page. Observed (Live Application): An additional "Generate PDF order" button is also present, which is not documented anywhere in the Requirement Analysis Report's functional requirements.</t>
+  </si>
+  <si>
+    <t>Discrepancy;UndocumentedFeature</t>
+  </si>
+  <si>
+    <t>Click "Generate PDF order"</t>
+  </si>
+  <si>
+    <t>Confirm the click does not error out or block the documented "Back Home" control from still functioning; record actual behavior (e.g., file download, new tab, no-op) as an evidence note for product-owner review, since no documented expected behavior exists for this control.</t>
+  </si>
+  <si>
+    <t>TC-031</t>
+  </si>
+  <si>
+    <t>DISCREPANCY: No quantity-selector control exists anywhere in the product/cart UI</t>
+  </si>
+  <si>
+    <t>Report Edge Cases (varying quantities)</t>
+  </si>
+  <si>
+    <t>Plan Discrepancy Note #9 (Intro)</t>
+  </si>
+  <si>
+    <t>Log in as standard_user, view a product's detail page and the inventory grid</t>
+  </si>
+  <si>
+    <t>No quantity input, stepper, or "+/-" control is present anywhere alongside "Add to cart"</t>
+  </si>
+  <si>
+    <t>Discrepancy;ScopeLimitation</t>
+  </si>
+  <si>
+    <t>Add the product to the cart and open the Cart page</t>
+  </si>
+  <si>
+    <t>Cart line item quantity is fixed at "1" with no control to increase or decrease it. Per Requirement (Expected): The Report's Edge Cases section anticipates verifying "varying quantities" arithmetic. Observed (Live Application): No UI path exists to create a quantity greater than 1 for a single line item, so that edge case cannot be executed as originally anticipated — confirmed as a scope limitation, not a defect against any specific FR.</t>
+  </si>
+  <si>
+    <t>TC-032</t>
+  </si>
+  <si>
+    <t>Cross-browser regression of the full checkout happy path (Chrome, Firefox, Safari)</t>
   </si>
   <si>
     <t>NFR1</t>
   </si>
   <si>
-    <t>N/A - QA Coverage Recommendation #8</t>
-  </si>
-  <si>
-    <t>Execute the TC-001 happy-path checkout flow on Chrome.</t>
-  </si>
-  <si>
-    <t>Full checkout flow completes with identical behavior/results to the Chrome baseline in TC-001.</t>
-  </si>
-  <si>
-    <t>Compatibility, Supplemental, Cross-Browser</t>
-  </si>
-  <si>
-    <t>Execute the TC-001 happy-path checkout flow on Firefox.</t>
-  </si>
-  <si>
-    <t>Full checkout flow completes with identical behavior/results.</t>
-  </si>
-  <si>
-    <t>Execute the TC-001 happy-path checkout flow on Safari/WebKit.</t>
-  </si>
-  <si>
-    <t>TC-031</t>
-  </si>
-  <si>
-    <t>[SUPPLEMENTAL] Exploratory Review of 'Secure' and 'Intuitive' Checkout Qualities</t>
-  </si>
-  <si>
-    <t>NFR3, NFR4</t>
-  </si>
-  <si>
-    <t>N/A - QA Coverage Recommendation #10</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Perform the full checkout flow while observing for any exposed sensitive data, non-HTTPS transitions, or session-handling concerns.</t>
-  </si>
-  <si>
-    <t>Observations recorded as findings; no pass/fail threshold is defined (NFR3, OQ3).</t>
-  </si>
-  <si>
-    <t>Exploratory, Supplemental, Security</t>
-  </si>
-  <si>
-    <t>Perform the full checkout flow while assessing clarity of feedback/messaging at each step.</t>
-  </si>
-  <si>
-    <t>Observations recorded as findings against NFR4 ('intuitive', 'clear feedback'); no measurable threshold is defined.</t>
-  </si>
-  <si>
-    <t>Exploratory, Supplemental, Usability</t>
+    <t>Derived — NFR1 (Recommendation #8)</t>
+  </si>
+  <si>
+    <t>Repeat the TC-001 full checkout flow (login -&gt; add to cart -&gt; cart -&gt; checkout info -&gt; overview -&gt; finish -&gt; back home) in Chrome</t>
+  </si>
+  <si>
+    <t>All TC-001 expected results hold identically in Chrome</t>
+  </si>
+  <si>
+    <t>NonFunctional;CrossBrowser</t>
+  </si>
+  <si>
+    <t>Repeat the same flow in Firefox</t>
+  </si>
+  <si>
+    <t>All TC-001 expected results hold identically in Firefox</t>
+  </si>
+  <si>
+    <t>Repeat the same flow in Safari (or WebKit-based equivalent)</t>
+  </si>
+  <si>
+    <t>All TC-001 expected results hold identically in Safari; any browser-specific rendering or functional deviation is recorded as a defect candidate</t>
+  </si>
+  <si>
+    <t>TC-033</t>
+  </si>
+  <si>
+    <t>Exploratory observation of checkout "security" controls</t>
+  </si>
+  <si>
+    <t>NFR3;OQ3</t>
+  </si>
+  <si>
+    <t>Derived — NFR3 (Recommendation #10)</t>
+  </si>
+  <si>
+    <t>Observe the protocol/scheme used to load every checkout-flow page (login, inventory, cart, checkout-step-one, checkout-step-two, checkout-complete)</t>
+  </si>
+  <si>
+    <t>Record whether HTTPS is used consistently; this is an observation, not a pass/fail assertion, since no concrete security control is documented (NFR3, OQ3)</t>
+  </si>
+  <si>
+    <t>Exploratory;NonFunctional;Security</t>
+  </si>
+  <si>
+    <t>Observe whether the checkout information fields (First Name, Last Name, Zip) are transmitted or rendered in any obviously insecure way (e.g., visible in plaintext URL parameters)</t>
+  </si>
+  <si>
+    <t>Record findings for product-owner review; flag any concerning observation as a candidate for a future, concretely-scoped security requirement rather than a confirmed defect against an undocumented standard</t>
+  </si>
+  <si>
+    <t>TC-034</t>
+  </si>
+  <si>
+    <t>Exploratory observation of checkout "intuitiveness" and step-by-step feedback clarity</t>
+  </si>
+  <si>
+    <t>NFR4;OQ3 (related)</t>
+  </si>
+  <si>
+    <t>Derived — NFR4 (Recommendation #10)</t>
+  </si>
+  <si>
+    <t>Walk through Cart -&gt; Checkout Info -&gt; Overview -&gt; Complete, noting whether each transition provides clear on-screen feedback of what just happened and what to do next</t>
+  </si>
+  <si>
+    <t>Record observations (e.g., error alert clarity, absence of a subtotal on the cart page per TC-005, Cancel-destination asymmetry per TC-026) as qualitative findings for product-owner review, not as pass/fail defects against a measurable NFR4 threshold</t>
+  </si>
+  <si>
+    <t>Exploratory;NonFunctional;Usability</t>
   </si>
 </sst>
 </file>
@@ -1170,20 +1191,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O54"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="60" customWidth="1"/>
-    <col min="4" max="4" width="38" customWidth="1"/>
-    <col min="5" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="4" max="4" width="37" customWidth="1"/>
+    <col min="5" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="11" width="60" customWidth="1"/>
-    <col min="12" max="12" width="38" customWidth="1"/>
+    <col min="9" max="10" width="60" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="49" customWidth="1"/>
+    <col min="15" max="15" width="48" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1250,26 +1271,26 @@
         <v>18</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2">
         <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1289,26 +1310,26 @@
         <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="2">
         <v>2</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1328,26 +1349,26 @@
         <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H4" s="2">
         <v>3</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1367,26 +1388,26 @@
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2">
         <v>4</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1406,26 +1427,26 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H6" s="2">
         <v>5</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1445,26 +1466,26 @@
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H7" s="2">
         <v>6</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1484,26 +1505,26 @@
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H8" s="2">
         <v>7</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1523,37 +1544,37 @@
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H9" s="2">
         <v>8</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" s="2">
         <v>1.2</v>
@@ -1562,37 +1583,37 @@
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D11" s="2">
         <v>1.2</v>
@@ -1601,10 +1622,10 @@
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H11" s="2">
         <v>2</v>
@@ -1620,18 +1641,18 @@
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D12" s="2">
         <v>1.2</v>
@@ -1640,10 +1661,10 @@
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H12" s="2">
         <v>3</v>
@@ -1659,18 +1680,18 @@
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D13" s="2">
         <v>1.2</v>
@@ -1679,10 +1700,10 @@
         <v>18</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H13" s="2">
         <v>4</v>
@@ -1698,18 +1719,18 @@
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="2">
         <v>1.2</v>
@@ -1718,16 +1739,16 @@
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H14" s="2">
         <v>5</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>48</v>
@@ -1737,7 +1758,7 @@
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1754,68 +1775,68 @@
         <v>2.1</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D16" s="2">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1832,800 +1853,784 @@
         <v>2.2</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H17" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
+      </c>
+      <c r="D18" s="2">
+        <v>2.2</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H18" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>72</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D19" s="2">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" s="2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D20" s="2">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D21" s="2">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H21" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
       <c r="O21" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="D22" s="2">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" s="2" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="D23" s="2">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>97</v>
+        <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
       <c r="O23" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D24" s="2">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>97</v>
+        <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H24" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="2" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
+      </c>
+      <c r="D25" s="2">
+        <v>3.5</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H25" s="2">
         <v>1</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>72</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
       <c r="O25" s="2" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>115</v>
+        <v>94</v>
+      </c>
+      <c r="D26" s="2">
+        <v>3.5</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H26" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>72</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" s="2" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>122</v>
+        <v>103</v>
+      </c>
+      <c r="D27" s="2">
+        <v>3.6</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H27" s="2">
         <v>1</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>72</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D28" s="2">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>97</v>
+        <v>18</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H28" s="2">
         <v>1</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" s="2" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="D29" s="2">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
       <c r="O29" s="2" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="D30" s="2">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H30" s="2">
         <v>1</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
       <c r="O30" s="2" t="s">
-        <v>55</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="D31" s="2">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
       <c r="O31" s="2" t="s">
-        <v>55</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="D32" s="2">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H32" s="2">
         <v>1</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>33</v>
+        <v>131</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
       <c r="O32" s="2" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="D33" s="2">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H33" s="2">
         <v>1</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>35</v>
+        <v>131</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
       <c r="O33" s="2" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="D34" s="2">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H34" s="2">
         <v>1</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
       <c r="O34" s="2" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="D35" s="2">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H35" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="O35" s="2" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="D36" s="2">
-        <v>6.1</v>
+        <v>5.2</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H36" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>168</v>
+        <v>36</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
       <c r="O36" s="2" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>174</v>
+        <v>151</v>
+      </c>
+      <c r="D37" s="2">
+        <v>5.3</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>18</v>
@@ -2634,41 +2639,37 @@
         <v>18</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H37" s="2">
         <v>1</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>72</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
       <c r="O37" s="2" t="s">
-        <v>178</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>174</v>
+        <v>151</v>
+      </c>
+      <c r="D38" s="2">
+        <v>5.3</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>18</v>
@@ -2677,667 +2678,1076 @@
         <v>18</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H38" s="2">
         <v>2</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>27</v>
+        <v>154</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>72</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
       <c r="O38" s="2" t="s">
-        <v>178</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>174</v>
+        <v>158</v>
+      </c>
+      <c r="D39" s="2">
+        <v>6.1</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H39" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>72</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
       <c r="O39" s="2" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>174</v>
+        <v>164</v>
+      </c>
+      <c r="D40" s="2">
+        <v>6.2</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H40" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>33</v>
+        <v>165</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>72</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
       <c r="O40" s="2" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
     </row>
     <row r="41" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="D41" s="2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>97</v>
+        <v>18</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H41" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>189</v>
+        <v>28</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>194</v>
+        <v>164</v>
+      </c>
+      <c r="D42" s="2">
+        <v>6.2</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H42" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>198</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
       <c r="O42" s="2" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>200</v>
+        <v>162</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>201</v>
+        <v>163</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>202</v>
+        <v>164</v>
       </c>
       <c r="D43" s="2">
-        <v>7.1</v>
+        <v>6.2</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H43" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>203</v>
+        <v>34</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>204</v>
+        <v>171</v>
       </c>
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
       <c r="O43" s="2" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>205</v>
+        <v>172</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>206</v>
+        <v>173</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>207</v>
+        <v>158</v>
+      </c>
+      <c r="D44" s="2">
+        <v>6.3</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H44" s="2">
         <v>1</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>208</v>
+        <v>174</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>72</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
       <c r="O44" s="2" t="s">
-        <v>211</v>
+        <v>176</v>
       </c>
     </row>
     <row r="45" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="D45" s="2">
-        <v>7.3</v>
+        <v>6.4</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>97</v>
+        <v>18</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="H45" s="2">
         <v>1</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>216</v>
+        <v>179</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>217</v>
+        <v>180</v>
       </c>
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
       <c r="O45" s="2" t="s">
-        <v>218</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>212</v>
+        <v>181</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>214</v>
+        <v>183</v>
       </c>
       <c r="D46" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="H46" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>220</v>
+        <v>74</v>
       </c>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
       <c r="O46" s="2" t="s">
-        <v>218</v>
+        <v>185</v>
       </c>
     </row>
     <row r="47" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>222</v>
+        <v>182</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>223</v>
+        <v>183</v>
       </c>
       <c r="D47" s="2">
-        <v>8.1</v>
+        <v>7.1</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H47" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>224</v>
+        <v>186</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>225</v>
+        <v>187</v>
       </c>
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2" t="s">
-        <v>226</v>
+        <v>185</v>
       </c>
     </row>
     <row r="48" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>221</v>
+        <v>188</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="D48" s="2">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H48" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>228</v>
+        <v>192</v>
       </c>
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="2" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>229</v>
+        <v>188</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>230</v>
+        <v>189</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>231</v>
+        <v>190</v>
       </c>
       <c r="D49" s="2">
-        <v>8.2</v>
+        <v>7.2</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H49" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>232</v>
+        <v>194</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>233</v>
+        <v>195</v>
       </c>
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
       <c r="O49" s="2" t="s">
-        <v>234</v>
+        <v>193</v>
       </c>
     </row>
     <row r="50" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>238</v>
+        <v>198</v>
+      </c>
+      <c r="D50" s="2">
+        <v>7.3</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H50" s="2">
         <v>1</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>239</v>
+        <v>199</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>240</v>
+        <v>147</v>
       </c>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
       <c r="O50" s="2" t="s">
-        <v>241</v>
+        <v>200</v>
       </c>
     </row>
     <row r="51" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>238</v>
+        <v>198</v>
+      </c>
+      <c r="D51" s="2">
+        <v>7.3</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H51" s="2">
         <v>2</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>242</v>
+        <v>201</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>243</v>
+        <v>202</v>
       </c>
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
       <c r="O51" s="2" t="s">
-        <v>241</v>
+        <v>200</v>
       </c>
     </row>
     <row r="52" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>238</v>
+        <v>198</v>
+      </c>
+      <c r="D52" s="2">
+        <v>7.3</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H52" s="2">
         <v>3</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>244</v>
+        <v>203</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>243</v>
+        <v>204</v>
       </c>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
       <c r="O52" s="2" t="s">
-        <v>241</v>
+        <v>200</v>
       </c>
     </row>
     <row r="53" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>248</v>
+        <v>207</v>
+      </c>
+      <c r="D53" s="2">
+        <v>8.1</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>249</v>
+        <v>59</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H53" s="2">
         <v>1</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>250</v>
+        <v>208</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>251</v>
+        <v>209</v>
       </c>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
       <c r="O53" s="2" t="s">
-        <v>252</v>
+        <v>210</v>
       </c>
     </row>
     <row r="54" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>248</v>
+        <v>207</v>
+      </c>
+      <c r="D54" s="2">
+        <v>8.1</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>249</v>
+        <v>59</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H54" s="2">
         <v>2</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>253</v>
+        <v>211</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>254</v>
+        <v>212</v>
       </c>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
       <c r="O54" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D55" s="2">
+        <v>8.2</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H55" s="2">
+        <v>1</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H56" s="2">
+        <v>1</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H57" s="2">
+        <v>2</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H58" s="2">
+        <v>1</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
+      <c r="M58" s="2"/>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H59" s="2">
+        <v>2</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H60" s="2">
+        <v>1</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
+      <c r="M60" s="2"/>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H61" s="2">
+        <v>2</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
+      <c r="M61" s="2"/>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H62" s="2">
+        <v>3</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H63" s="2">
+        <v>1</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H64" s="2">
+        <v>2</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J64" s="2" t="s">
         <v>255</v>
+      </c>
+      <c r="K64" s="2"/>
+      <c r="L64" s="2"/>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H65" s="2">
+        <v>1</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>
